--- a/游戏设计王/老虎机数学入门-PartIII-Wild连线模型.xlsx
+++ b/游戏设计王/老虎机数学入门-PartIII-Wild连线模型.xlsx
@@ -495,11 +495,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -1198,7 +1199,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1287,6 +1288,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -7172,7 +7176,7 @@
       <c r="A49" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B49" s="16">
+      <c r="B49" s="44">
         <f>SUM(L52:L299)</f>
         <v>1.630853125</v>
       </c>
@@ -7312,7 +7316,7 @@
         <f>PRODUCT($B$39,$C$39,$D$39,$E$39,$F$39)</f>
         <v>81</v>
       </c>
-      <c r="J52" s="19">
+      <c r="J52" s="45">
         <f t="shared" ref="J52:J66" si="5">I52/$B$48</f>
         <v>2.53125e-5</v>
       </c>
@@ -7320,7 +7324,7 @@
         <f t="shared" ref="K52:K66" si="6">INDEX($B$3:$D$7,MATCH($B52,$A$3:$A$7,0),MATCH($C52,$B$2:$D$2,0))</f>
         <v>100</v>
       </c>
-      <c r="L52" s="19">
+      <c r="L52" s="45">
         <f t="shared" ref="L52:L66" si="7">J52*K52</f>
         <v>0.00253125</v>
       </c>
@@ -7354,7 +7358,7 @@
         <f>PRODUCT($B$39,$C$39,$D$39,$E$39,($F$45-$F$38-$F$39))</f>
         <v>405</v>
       </c>
-      <c r="J53" s="19">
+      <c r="J53" s="45">
         <f t="shared" si="5"/>
         <v>0.0001265625</v>
       </c>
@@ -7362,7 +7366,7 @@
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
-      <c r="L53" s="19">
+      <c r="L53" s="45">
         <f t="shared" si="7"/>
         <v>0.003796875</v>
       </c>
@@ -7396,7 +7400,7 @@
         <f>PRODUCT($B$39,$C$39,$D$39,($E$45-$E$38-$E$39),$F$45)</f>
         <v>2700</v>
       </c>
-      <c r="J54" s="19">
+      <c r="J54" s="45">
         <f t="shared" si="5"/>
         <v>0.00084375</v>
       </c>
@@ -7404,7 +7408,7 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L54" s="19">
+      <c r="L54" s="45">
         <f t="shared" si="7"/>
         <v>0.00421875</v>
       </c>
@@ -7438,7 +7442,7 @@
         <f>PRODUCT($B$40,$C$40,$D$40,$E$40,$F$40)</f>
         <v>162</v>
       </c>
-      <c r="J55" s="19">
+      <c r="J55" s="45">
         <f t="shared" si="5"/>
         <v>5.0625e-5</v>
       </c>
@@ -7446,7 +7450,7 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
-      <c r="L55" s="19">
+      <c r="L55" s="45">
         <f t="shared" si="7"/>
         <v>0.0050625</v>
       </c>
@@ -7480,7 +7484,7 @@
         <f>PRODUCT($B$40,$C$40,$D$40,$E$40,($F$45-$F$38-$F$40))</f>
         <v>810</v>
       </c>
-      <c r="J56" s="19">
+      <c r="J56" s="45">
         <f t="shared" si="5"/>
         <v>0.000253125</v>
       </c>
@@ -7488,7 +7492,7 @@
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="L56" s="19">
+      <c r="L56" s="45">
         <f t="shared" si="7"/>
         <v>0.006328125</v>
       </c>
@@ -7522,7 +7526,7 @@
         <f>PRODUCT($B$40,$C$40,$D$40,($E$45-$E$38-$E$40),$F$45)</f>
         <v>5400</v>
       </c>
-      <c r="J57" s="19">
+      <c r="J57" s="45">
         <f t="shared" si="5"/>
         <v>0.0016875</v>
       </c>
@@ -7530,7 +7534,7 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L57" s="19">
+      <c r="L57" s="45">
         <f t="shared" si="7"/>
         <v>0.0084375</v>
       </c>
@@ -7564,7 +7568,7 @@
         <f>PRODUCT($B$41,$C$41,$D$41,$E$41,$F$41)</f>
         <v>1280</v>
       </c>
-      <c r="J58" s="19">
+      <c r="J58" s="45">
         <f t="shared" si="5"/>
         <v>0.0004</v>
       </c>
@@ -7572,7 +7576,7 @@
         <f t="shared" si="6"/>
         <v>75</v>
       </c>
-      <c r="L58" s="19">
+      <c r="L58" s="45">
         <f t="shared" si="7"/>
         <v>0.03</v>
       </c>
@@ -7606,7 +7610,7 @@
         <f>PRODUCT($B$41,$C$41,$D$41,$E$41,($F$45-$F$38-$F$41))</f>
         <v>4480</v>
       </c>
-      <c r="J59" s="19">
+      <c r="J59" s="45">
         <f t="shared" si="5"/>
         <v>0.0014</v>
       </c>
@@ -7614,7 +7618,7 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="L59" s="19">
+      <c r="L59" s="45">
         <f t="shared" si="7"/>
         <v>0.028</v>
       </c>
@@ -7648,7 +7652,7 @@
         <f>PRODUCT($B$41,$C$41,$D$41,($E$45-$E$38-$E$41),$F$45)</f>
         <v>22400</v>
       </c>
-      <c r="J60" s="19">
+      <c r="J60" s="45">
         <f t="shared" si="5"/>
         <v>0.007</v>
       </c>
@@ -7656,7 +7660,7 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L60" s="19">
+      <c r="L60" s="45">
         <f t="shared" si="7"/>
         <v>0.035</v>
       </c>
@@ -7690,7 +7694,7 @@
         <f>PRODUCT($B$42,$C$42,$D$42,$E$42,$F$42)</f>
         <v>960</v>
       </c>
-      <c r="J61" s="19">
+      <c r="J61" s="45">
         <f t="shared" si="5"/>
         <v>0.0003</v>
       </c>
@@ -7698,7 +7702,7 @@
         <f t="shared" si="6"/>
         <v>75</v>
       </c>
-      <c r="L61" s="19">
+      <c r="L61" s="45">
         <f t="shared" si="7"/>
         <v>0.0225</v>
       </c>
@@ -7732,7 +7736,7 @@
         <f>PRODUCT($B$42,$C$42,$D$42,$E$42,($F$45-$F$38-$F$42))</f>
         <v>3360</v>
       </c>
-      <c r="J62" s="19">
+      <c r="J62" s="45">
         <f t="shared" si="5"/>
         <v>0.00105</v>
       </c>
@@ -7740,7 +7744,7 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="L62" s="19">
+      <c r="L62" s="45">
         <f t="shared" si="7"/>
         <v>0.021</v>
       </c>
@@ -7774,7 +7778,7 @@
         <f>PRODUCT($B$42,$C$42,$D$42,($E$45-$E$38-$E$42),$F$45)</f>
         <v>16800</v>
       </c>
-      <c r="J63" s="19">
+      <c r="J63" s="45">
         <f t="shared" si="5"/>
         <v>0.00525</v>
       </c>
@@ -7782,7 +7786,7 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L63" s="19">
+      <c r="L63" s="45">
         <f t="shared" si="7"/>
         <v>0.02625</v>
       </c>
@@ -7816,7 +7820,7 @@
         <f>PRODUCT($B$43,$C$43,$D$43,$E$43,$F$43)</f>
         <v>1536</v>
       </c>
-      <c r="J64" s="19">
+      <c r="J64" s="45">
         <f t="shared" si="5"/>
         <v>0.00048</v>
       </c>
@@ -7824,7 +7828,7 @@
         <f t="shared" si="6"/>
         <v>50</v>
       </c>
-      <c r="L64" s="19">
+      <c r="L64" s="45">
         <f t="shared" si="7"/>
         <v>0.024</v>
       </c>
@@ -7858,7 +7862,7 @@
         <f>PRODUCT($B$43,$C$43,$D$43,$E$43,($F$45-$F$38-$F$43))</f>
         <v>5376</v>
       </c>
-      <c r="J65" s="19">
+      <c r="J65" s="45">
         <f t="shared" si="5"/>
         <v>0.00168</v>
       </c>
@@ -7866,7 +7870,7 @@
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="L65" s="19">
+      <c r="L65" s="45">
         <f t="shared" si="7"/>
         <v>0.0168</v>
       </c>
@@ -7900,7 +7904,7 @@
         <f>PRODUCT($B$43,$C$43,$D$43,($E$45-$E$38-$E$43),$F$45)</f>
         <v>26880</v>
       </c>
-      <c r="J66" s="19">
+      <c r="J66" s="45">
         <f t="shared" si="5"/>
         <v>0.0084</v>
       </c>
@@ -7908,7 +7912,7 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L66" s="19">
+      <c r="L66" s="45">
         <f t="shared" si="7"/>
         <v>0.042</v>
       </c>
@@ -7942,7 +7946,7 @@
         <f>PRODUCT($B$38,$C$38,$D$39,$E$38,$F$38)</f>
         <v>48</v>
       </c>
-      <c r="J67" s="19">
+      <c r="J67" s="45">
         <f t="shared" ref="J67:J112" si="8">I67/$B$48</f>
         <v>1.5e-5</v>
       </c>
@@ -7950,7 +7954,7 @@
         <f t="shared" ref="K67:K93" si="9">MAX(0,INDEX($B$3:$D$7,MATCH($B67,$A$3:$A$7,0),MATCH($C67,$B$2:$D$2,0)))</f>
         <v>100</v>
       </c>
-      <c r="L67" s="19">
+      <c r="L67" s="45">
         <f t="shared" ref="L67:L112" si="10">J67*K67</f>
         <v>0.0015</v>
       </c>
@@ -7984,7 +7988,7 @@
         <f>PRODUCT($B$38,$C$38,$D$39,$E$38,$F$39)</f>
         <v>72</v>
       </c>
-      <c r="J68" s="19">
+      <c r="J68" s="45">
         <f t="shared" si="8"/>
         <v>2.25e-5</v>
       </c>
@@ -7992,7 +7996,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L68" s="19">
+      <c r="L68" s="45">
         <f t="shared" si="10"/>
         <v>0.00225</v>
       </c>
@@ -8026,7 +8030,7 @@
         <f>PRODUCT($B$38,$C$38,$D$39,$E$39,$F$38)</f>
         <v>72</v>
       </c>
-      <c r="J69" s="19">
+      <c r="J69" s="45">
         <f t="shared" si="8"/>
         <v>2.25e-5</v>
       </c>
@@ -8034,7 +8038,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L69" s="19">
+      <c r="L69" s="45">
         <f t="shared" si="10"/>
         <v>0.00225</v>
       </c>
@@ -8068,7 +8072,7 @@
         <f>PRODUCT($B$38,$C$38,$D$39,$E$39,$F$39)</f>
         <v>108</v>
       </c>
-      <c r="J70" s="19">
+      <c r="J70" s="45">
         <f t="shared" si="8"/>
         <v>3.375e-5</v>
       </c>
@@ -8076,7 +8080,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L70" s="19">
+      <c r="L70" s="45">
         <f t="shared" si="10"/>
         <v>0.003375</v>
       </c>
@@ -8110,7 +8114,7 @@
         <f>PRODUCT($B$38,$C$39,$D$38,$E$38,$F$38)</f>
         <v>48</v>
       </c>
-      <c r="J71" s="19">
+      <c r="J71" s="45">
         <f t="shared" si="8"/>
         <v>1.5e-5</v>
       </c>
@@ -8118,7 +8122,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L71" s="19">
+      <c r="L71" s="45">
         <f t="shared" si="10"/>
         <v>0.0015</v>
       </c>
@@ -8152,7 +8156,7 @@
         <f>PRODUCT($B$38,$C$39,$D$38,$E$38,$F$39)</f>
         <v>72</v>
       </c>
-      <c r="J72" s="19">
+      <c r="J72" s="45">
         <f t="shared" si="8"/>
         <v>2.25e-5</v>
       </c>
@@ -8160,7 +8164,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L72" s="19">
+      <c r="L72" s="45">
         <f t="shared" si="10"/>
         <v>0.00225</v>
       </c>
@@ -8194,7 +8198,7 @@
         <f>PRODUCT($B$38,$C$39,$D$38,$E$39,$F$38)</f>
         <v>72</v>
       </c>
-      <c r="J73" s="19">
+      <c r="J73" s="45">
         <f t="shared" si="8"/>
         <v>2.25e-5</v>
       </c>
@@ -8202,7 +8206,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L73" s="19">
+      <c r="L73" s="45">
         <f t="shared" si="10"/>
         <v>0.00225</v>
       </c>
@@ -8236,7 +8240,7 @@
         <f>PRODUCT($B$38,$C$39,$D$38,$E$39,$F$39)</f>
         <v>108</v>
       </c>
-      <c r="J74" s="19">
+      <c r="J74" s="45">
         <f t="shared" si="8"/>
         <v>3.375e-5</v>
       </c>
@@ -8244,7 +8248,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L74" s="19">
+      <c r="L74" s="45">
         <f t="shared" si="10"/>
         <v>0.003375</v>
       </c>
@@ -8278,7 +8282,7 @@
         <f>PRODUCT($B$38,$C$39,$D$39,$E$38,$F$38)</f>
         <v>72</v>
       </c>
-      <c r="J75" s="19">
+      <c r="J75" s="45">
         <f t="shared" si="8"/>
         <v>2.25e-5</v>
       </c>
@@ -8286,7 +8290,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L75" s="19">
+      <c r="L75" s="45">
         <f t="shared" si="10"/>
         <v>0.00225</v>
       </c>
@@ -8320,7 +8324,7 @@
         <f>PRODUCT($B$38,$C$39,$D$39,$E$38,$F$39)</f>
         <v>108</v>
       </c>
-      <c r="J76" s="19">
+      <c r="J76" s="45">
         <f t="shared" si="8"/>
         <v>3.375e-5</v>
       </c>
@@ -8328,7 +8332,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L76" s="19">
+      <c r="L76" s="45">
         <f t="shared" si="10"/>
         <v>0.003375</v>
       </c>
@@ -8362,7 +8366,7 @@
         <f>PRODUCT($B$38,$C$39,$D$39,$E$39,$F$38)</f>
         <v>108</v>
       </c>
-      <c r="J77" s="19">
+      <c r="J77" s="45">
         <f t="shared" si="8"/>
         <v>3.375e-5</v>
       </c>
@@ -8370,7 +8374,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L77" s="19">
+      <c r="L77" s="45">
         <f t="shared" si="10"/>
         <v>0.003375</v>
       </c>
@@ -8404,7 +8408,7 @@
         <f>PRODUCT($B$38,$C$39,$D$39,$E$39,$F$39)</f>
         <v>162</v>
       </c>
-      <c r="J78" s="19">
+      <c r="J78" s="45">
         <f t="shared" si="8"/>
         <v>5.0625e-5</v>
       </c>
@@ -8412,7 +8416,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L78" s="19">
+      <c r="L78" s="45">
         <f t="shared" si="10"/>
         <v>0.0050625</v>
       </c>
@@ -8446,7 +8450,7 @@
         <f>PRODUCT($B$39,$C$38,$D$38,$E$38,$F$38)</f>
         <v>16</v>
       </c>
-      <c r="J79" s="19">
+      <c r="J79" s="45">
         <f t="shared" si="8"/>
         <v>5e-6</v>
       </c>
@@ -8454,7 +8458,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L79" s="19">
+      <c r="L79" s="45">
         <f t="shared" si="10"/>
         <v>0.0005</v>
       </c>
@@ -8488,7 +8492,7 @@
         <f>PRODUCT($B$39,$C$38,$D$38,$E$38,$F$39)</f>
         <v>24</v>
       </c>
-      <c r="J80" s="19">
+      <c r="J80" s="45">
         <f t="shared" si="8"/>
         <v>7.5e-6</v>
       </c>
@@ -8496,7 +8500,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L80" s="19">
+      <c r="L80" s="45">
         <f t="shared" si="10"/>
         <v>0.00075</v>
       </c>
@@ -8530,7 +8534,7 @@
         <f>PRODUCT($B$39,$C$38,$D$38,$E$39,$F$38)</f>
         <v>24</v>
       </c>
-      <c r="J81" s="19">
+      <c r="J81" s="45">
         <f t="shared" si="8"/>
         <v>7.5e-6</v>
       </c>
@@ -8538,7 +8542,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L81" s="19">
+      <c r="L81" s="45">
         <f t="shared" si="10"/>
         <v>0.00075</v>
       </c>
@@ -8572,7 +8576,7 @@
         <f>PRODUCT($B$39,$C$38,$D$38,$E$39,$F$39)</f>
         <v>36</v>
       </c>
-      <c r="J82" s="19">
+      <c r="J82" s="45">
         <f t="shared" si="8"/>
         <v>1.125e-5</v>
       </c>
@@ -8580,7 +8584,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L82" s="19">
+      <c r="L82" s="45">
         <f t="shared" si="10"/>
         <v>0.001125</v>
       </c>
@@ -8614,7 +8618,7 @@
         <f>PRODUCT($B$39,$C$38,$D$39,$E$38,$F$38)</f>
         <v>24</v>
       </c>
-      <c r="J83" s="19">
+      <c r="J83" s="45">
         <f t="shared" si="8"/>
         <v>7.5e-6</v>
       </c>
@@ -8622,7 +8626,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L83" s="19">
+      <c r="L83" s="45">
         <f t="shared" si="10"/>
         <v>0.00075</v>
       </c>
@@ -8656,7 +8660,7 @@
         <f>PRODUCT($B$39,$C$38,$D$39,$E$38,$F$39)</f>
         <v>36</v>
       </c>
-      <c r="J84" s="19">
+      <c r="J84" s="45">
         <f t="shared" si="8"/>
         <v>1.125e-5</v>
       </c>
@@ -8664,7 +8668,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L84" s="19">
+      <c r="L84" s="45">
         <f t="shared" si="10"/>
         <v>0.001125</v>
       </c>
@@ -8698,7 +8702,7 @@
         <f>PRODUCT($B$39,$C$38,$D$39,$E$39,$F$38)</f>
         <v>36</v>
       </c>
-      <c r="J85" s="19">
+      <c r="J85" s="45">
         <f t="shared" si="8"/>
         <v>1.125e-5</v>
       </c>
@@ -8706,7 +8710,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L85" s="19">
+      <c r="L85" s="45">
         <f t="shared" si="10"/>
         <v>0.001125</v>
       </c>
@@ -8740,7 +8744,7 @@
         <f>PRODUCT($B$39,$C$38,$D$39,$E$39,$F$39)</f>
         <v>54</v>
       </c>
-      <c r="J86" s="19">
+      <c r="J86" s="45">
         <f t="shared" si="8"/>
         <v>1.6875e-5</v>
       </c>
@@ -8748,7 +8752,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L86" s="19">
+      <c r="L86" s="45">
         <f t="shared" si="10"/>
         <v>0.0016875</v>
       </c>
@@ -8782,7 +8786,7 @@
         <f>PRODUCT($B$39,$C$39,$D$38,$E$38,$F$38)</f>
         <v>24</v>
       </c>
-      <c r="J87" s="19">
+      <c r="J87" s="45">
         <f t="shared" si="8"/>
         <v>7.5e-6</v>
       </c>
@@ -8790,7 +8794,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L87" s="19">
+      <c r="L87" s="45">
         <f t="shared" si="10"/>
         <v>0.00075</v>
       </c>
@@ -8824,7 +8828,7 @@
         <f>PRODUCT($B$39,$C$39,$D$38,$E$38,$F$39)</f>
         <v>36</v>
       </c>
-      <c r="J88" s="19">
+      <c r="J88" s="45">
         <f t="shared" si="8"/>
         <v>1.125e-5</v>
       </c>
@@ -8832,7 +8836,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L88" s="19">
+      <c r="L88" s="45">
         <f t="shared" si="10"/>
         <v>0.001125</v>
       </c>
@@ -8866,7 +8870,7 @@
         <f>PRODUCT($B$39,$C$39,$D$38,$E$39,$F$38)</f>
         <v>36</v>
       </c>
-      <c r="J89" s="19">
+      <c r="J89" s="45">
         <f t="shared" si="8"/>
         <v>1.125e-5</v>
       </c>
@@ -8874,7 +8878,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L89" s="19">
+      <c r="L89" s="45">
         <f t="shared" si="10"/>
         <v>0.001125</v>
       </c>
@@ -8908,7 +8912,7 @@
         <f>PRODUCT($B$39,$C$39,$D$38,$E$39,$F$39)</f>
         <v>54</v>
       </c>
-      <c r="J90" s="19">
+      <c r="J90" s="45">
         <f t="shared" si="8"/>
         <v>1.6875e-5</v>
       </c>
@@ -8916,7 +8920,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L90" s="19">
+      <c r="L90" s="45">
         <f t="shared" si="10"/>
         <v>0.0016875</v>
       </c>
@@ -8950,7 +8954,7 @@
         <f>PRODUCT($B$39,$C$39,$D$39,$E$38,$F$38)</f>
         <v>36</v>
       </c>
-      <c r="J91" s="19">
+      <c r="J91" s="45">
         <f t="shared" si="8"/>
         <v>1.125e-5</v>
       </c>
@@ -8958,7 +8962,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L91" s="19">
+      <c r="L91" s="45">
         <f t="shared" si="10"/>
         <v>0.001125</v>
       </c>
@@ -8992,7 +8996,7 @@
         <f>PRODUCT($B$39,$C$39,$D$39,$E$38,$F$39)</f>
         <v>54</v>
       </c>
-      <c r="J92" s="19">
+      <c r="J92" s="45">
         <f t="shared" si="8"/>
         <v>1.6875e-5</v>
       </c>
@@ -9000,7 +9004,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L92" s="19">
+      <c r="L92" s="45">
         <f t="shared" si="10"/>
         <v>0.0016875</v>
       </c>
@@ -9034,7 +9038,7 @@
         <f>PRODUCT($B$39,$C$39,$D$39,$E$39,$F$38)</f>
         <v>54</v>
       </c>
-      <c r="J93" s="19">
+      <c r="J93" s="45">
         <f t="shared" si="8"/>
         <v>1.6875e-5</v>
       </c>
@@ -9042,7 +9046,7 @@
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="L93" s="19">
+      <c r="L93" s="45">
         <f t="shared" si="10"/>
         <v>0.0016875</v>
       </c>
@@ -9076,7 +9080,7 @@
         <f>PRODUCT($B$38,$C$38,$D$39,$E$38,($F$45-$F$38-$F$39))</f>
         <v>360</v>
       </c>
-      <c r="J94" s="19">
+      <c r="J94" s="45">
         <f t="shared" si="8"/>
         <v>0.0001125</v>
       </c>
@@ -9084,7 +9088,7 @@
         <f t="shared" ref="K94:K106" si="11">MAX(0,INDEX($B$3:$D$7,MATCH($B94,$A$3:$A$7,0),MATCH($C94,$B$2:$D$2,0)))</f>
         <v>30</v>
       </c>
-      <c r="L94" s="19">
+      <c r="L94" s="45">
         <f t="shared" si="10"/>
         <v>0.003375</v>
       </c>
@@ -9118,7 +9122,7 @@
         <f>PRODUCT($B$38,$C$38,$D$39,$E$39,($F$45-$F$38-$F$39))</f>
         <v>540</v>
       </c>
-      <c r="J95" s="19">
+      <c r="J95" s="45">
         <f t="shared" si="8"/>
         <v>0.00016875</v>
       </c>
@@ -9126,7 +9130,7 @@
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="L95" s="19">
+      <c r="L95" s="45">
         <f t="shared" si="10"/>
         <v>0.0050625</v>
       </c>
@@ -9160,7 +9164,7 @@
         <f>PRODUCT($B$38,$C$39,$D$38,$E$38,($F$45-$F$38-$F$39))</f>
         <v>360</v>
       </c>
-      <c r="J96" s="19">
+      <c r="J96" s="45">
         <f t="shared" si="8"/>
         <v>0.0001125</v>
       </c>
@@ -9168,7 +9172,7 @@
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="L96" s="19">
+      <c r="L96" s="45">
         <f t="shared" si="10"/>
         <v>0.003375</v>
       </c>
@@ -9202,7 +9206,7 @@
         <f>PRODUCT($B$38,$C$39,$D$38,$E$39,($F$45-$F$38-$F$39))</f>
         <v>540</v>
       </c>
-      <c r="J97" s="19">
+      <c r="J97" s="45">
         <f t="shared" si="8"/>
         <v>0.00016875</v>
       </c>
@@ -9210,7 +9214,7 @@
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="L97" s="19">
+      <c r="L97" s="45">
         <f t="shared" si="10"/>
         <v>0.0050625</v>
       </c>
@@ -9244,7 +9248,7 @@
         <f>PRODUCT($B$38,$C$39,$D$39,$E$38,($F$45-$F$38-$F$39))</f>
         <v>540</v>
       </c>
-      <c r="J98" s="19">
+      <c r="J98" s="45">
         <f t="shared" si="8"/>
         <v>0.00016875</v>
       </c>
@@ -9252,7 +9256,7 @@
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="L98" s="19">
+      <c r="L98" s="45">
         <f t="shared" si="10"/>
         <v>0.0050625</v>
       </c>
@@ -9286,7 +9290,7 @@
         <f>PRODUCT($B$38,$C$39,$D$39,$E$39,($F$45-$F$38-$F$39))</f>
         <v>810</v>
       </c>
-      <c r="J99" s="19">
+      <c r="J99" s="45">
         <f t="shared" si="8"/>
         <v>0.000253125</v>
       </c>
@@ -9294,7 +9298,7 @@
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="L99" s="19">
+      <c r="L99" s="45">
         <f t="shared" si="10"/>
         <v>0.00759375</v>
       </c>
@@ -9328,7 +9332,7 @@
         <f>PRODUCT($B$39,$C$38,$D$38,$E$38,($F$45-$F$38-$F$39))</f>
         <v>120</v>
       </c>
-      <c r="J100" s="19">
+      <c r="J100" s="45">
         <f t="shared" si="8"/>
         <v>3.75e-5</v>
       </c>
@@ -9336,7 +9340,7 @@
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="L100" s="19">
+      <c r="L100" s="45">
         <f t="shared" si="10"/>
         <v>0.001125</v>
       </c>
@@ -9370,7 +9374,7 @@
         <f>PRODUCT($B$39,$C$38,$D$38,$E$39,($F$45-$F$38-$F$39))</f>
         <v>180</v>
       </c>
-      <c r="J101" s="19">
+      <c r="J101" s="45">
         <f t="shared" si="8"/>
         <v>5.625e-5</v>
       </c>
@@ -9378,7 +9382,7 @@
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="L101" s="19">
+      <c r="L101" s="45">
         <f t="shared" si="10"/>
         <v>0.0016875</v>
       </c>
@@ -9412,7 +9416,7 @@
         <f>PRODUCT($B$39,$C$38,$D$39,$E$38,($F$45-$F$38-$F$39))</f>
         <v>180</v>
       </c>
-      <c r="J102" s="19">
+      <c r="J102" s="45">
         <f t="shared" si="8"/>
         <v>5.625e-5</v>
       </c>
@@ -9420,7 +9424,7 @@
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="L102" s="19">
+      <c r="L102" s="45">
         <f t="shared" si="10"/>
         <v>0.0016875</v>
       </c>
@@ -9454,7 +9458,7 @@
         <f>PRODUCT($B$39,$C$38,$D$39,$E$39,($F$45-$F$38-$F$39))</f>
         <v>270</v>
       </c>
-      <c r="J103" s="19">
+      <c r="J103" s="45">
         <f t="shared" si="8"/>
         <v>8.4375e-5</v>
       </c>
@@ -9462,7 +9466,7 @@
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="L103" s="19">
+      <c r="L103" s="45">
         <f t="shared" si="10"/>
         <v>0.00253125</v>
       </c>
@@ -9496,7 +9500,7 @@
         <f>PRODUCT($B$39,$C$39,$D$38,$E$38,($F$45-$F$38-$F$39))</f>
         <v>180</v>
       </c>
-      <c r="J104" s="19">
+      <c r="J104" s="45">
         <f t="shared" si="8"/>
         <v>5.625e-5</v>
       </c>
@@ -9504,7 +9508,7 @@
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="L104" s="19">
+      <c r="L104" s="45">
         <f t="shared" si="10"/>
         <v>0.0016875</v>
       </c>
@@ -9538,7 +9542,7 @@
         <f>PRODUCT($B$39,$C$39,$D$38,$E$39,($F$45-$F$38-$F$39))</f>
         <v>270</v>
       </c>
-      <c r="J105" s="19">
+      <c r="J105" s="45">
         <f t="shared" si="8"/>
         <v>8.4375e-5</v>
       </c>
@@ -9546,7 +9550,7 @@
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="L105" s="19">
+      <c r="L105" s="45">
         <f t="shared" si="10"/>
         <v>0.00253125</v>
       </c>
@@ -9580,7 +9584,7 @@
         <f>PRODUCT($B$39,$C$39,$D$39,$E$38,($F$45-$F$38-$F$39))</f>
         <v>270</v>
       </c>
-      <c r="J106" s="19">
+      <c r="J106" s="45">
         <f t="shared" si="8"/>
         <v>8.4375e-5</v>
       </c>
@@ -9588,7 +9592,7 @@
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="L106" s="19">
+      <c r="L106" s="45">
         <f t="shared" si="10"/>
         <v>0.00253125</v>
       </c>
@@ -9622,7 +9626,7 @@
         <f>PRODUCT($B$38,$C$38,$D$39,($E$45-$E$38-$E$39),$F$45)</f>
         <v>3600</v>
       </c>
-      <c r="J107" s="19">
+      <c r="J107" s="45">
         <f t="shared" si="8"/>
         <v>0.001125</v>
       </c>
@@ -9630,7 +9634,7 @@
         <f t="shared" ref="K107:K112" si="12">MAX(0,INDEX($B$3:$D$7,MATCH($B107,$A$3:$A$7,0),MATCH($C107,$B$2:$D$2,0)))</f>
         <v>5</v>
       </c>
-      <c r="L107" s="19">
+      <c r="L107" s="45">
         <f t="shared" si="10"/>
         <v>0.005625</v>
       </c>
@@ -9664,7 +9668,7 @@
         <f>PRODUCT($B$38,$C$39,$D$38,($E$45-$E$38-$E$39),$F$45)</f>
         <v>3600</v>
       </c>
-      <c r="J108" s="19">
+      <c r="J108" s="45">
         <f t="shared" si="8"/>
         <v>0.001125</v>
       </c>
@@ -9672,7 +9676,7 @@
         <f t="shared" si="12"/>
         <v>5</v>
       </c>
-      <c r="L108" s="19">
+      <c r="L108" s="45">
         <f t="shared" si="10"/>
         <v>0.005625</v>
       </c>
@@ -9706,7 +9710,7 @@
         <f>PRODUCT($B$38,$C$39,$D$39,($E$45-$E$38-$E$39),$F$45)</f>
         <v>5400</v>
       </c>
-      <c r="J109" s="19">
+      <c r="J109" s="45">
         <f t="shared" si="8"/>
         <v>0.0016875</v>
       </c>
@@ -9714,7 +9718,7 @@
         <f t="shared" si="12"/>
         <v>5</v>
       </c>
-      <c r="L109" s="19">
+      <c r="L109" s="45">
         <f t="shared" si="10"/>
         <v>0.0084375</v>
       </c>
@@ -9748,7 +9752,7 @@
         <f>PRODUCT($B$39,$C$38,$D$38,($E$45-$E$38-$E$39),$F$45)</f>
         <v>1200</v>
       </c>
-      <c r="J110" s="19">
+      <c r="J110" s="45">
         <f t="shared" si="8"/>
         <v>0.000375</v>
       </c>
@@ -9756,7 +9760,7 @@
         <f t="shared" si="12"/>
         <v>5</v>
       </c>
-      <c r="L110" s="19">
+      <c r="L110" s="45">
         <f t="shared" si="10"/>
         <v>0.001875</v>
       </c>
@@ -9790,7 +9794,7 @@
         <f>PRODUCT($B$39,$C$38,$D$39,($E$45-$E$38-$E$39),$F$45)</f>
         <v>1800</v>
       </c>
-      <c r="J111" s="19">
+      <c r="J111" s="45">
         <f t="shared" si="8"/>
         <v>0.0005625</v>
       </c>
@@ -9798,7 +9802,7 @@
         <f t="shared" si="12"/>
         <v>5</v>
       </c>
-      <c r="L111" s="19">
+      <c r="L111" s="45">
         <f t="shared" si="10"/>
         <v>0.0028125</v>
       </c>
@@ -9832,7 +9836,7 @@
         <f>PRODUCT($B$39,$C$39,$D$38,($E$45-$E$38-$E$39),$F$45)</f>
         <v>1800</v>
       </c>
-      <c r="J112" s="19">
+      <c r="J112" s="45">
         <f t="shared" si="8"/>
         <v>0.0005625</v>
       </c>
@@ -9840,7 +9844,7 @@
         <f t="shared" si="12"/>
         <v>5</v>
       </c>
-      <c r="L112" s="19">
+      <c r="L112" s="45">
         <f t="shared" si="10"/>
         <v>0.0028125</v>
       </c>
@@ -9874,7 +9878,7 @@
         <f>PRODUCT($B$38,$C$38,$D$40,$E$38,$F$38)</f>
         <v>48</v>
       </c>
-      <c r="J113" s="19">
+      <c r="J113" s="45">
         <f t="shared" ref="J113:J176" si="13">I113/$B$48</f>
         <v>1.5e-5</v>
       </c>
@@ -9882,7 +9886,7 @@
         <f t="shared" ref="K113:K139" si="14">MAX(0,INDEX($B$3:$D$7,MATCH($B113,$A$3:$A$7,0),MATCH($C113,$B$2:$D$2,0)))</f>
         <v>100</v>
       </c>
-      <c r="L113" s="19">
+      <c r="L113" s="45">
         <f t="shared" ref="L113:L176" si="15">J113*K113</f>
         <v>0.0015</v>
       </c>
@@ -9916,7 +9920,7 @@
         <f>PRODUCT($B$38,$C$38,$D$40,$E$38,$F$40)</f>
         <v>72</v>
       </c>
-      <c r="J114" s="19">
+      <c r="J114" s="45">
         <f t="shared" si="13"/>
         <v>2.25e-5</v>
       </c>
@@ -9924,7 +9928,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L114" s="19">
+      <c r="L114" s="45">
         <f t="shared" si="15"/>
         <v>0.00225</v>
       </c>
@@ -9958,7 +9962,7 @@
         <f>PRODUCT($B$38,$C$38,$D$40,$E$40,$F$38)</f>
         <v>72</v>
       </c>
-      <c r="J115" s="19">
+      <c r="J115" s="45">
         <f t="shared" si="13"/>
         <v>2.25e-5</v>
       </c>
@@ -9966,7 +9970,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L115" s="19">
+      <c r="L115" s="45">
         <f t="shared" si="15"/>
         <v>0.00225</v>
       </c>
@@ -10000,7 +10004,7 @@
         <f>PRODUCT($B$38,$C$38,$D$40,$E$40,$F$40)</f>
         <v>108</v>
       </c>
-      <c r="J116" s="19">
+      <c r="J116" s="45">
         <f t="shared" si="13"/>
         <v>3.375e-5</v>
       </c>
@@ -10008,7 +10012,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L116" s="19">
+      <c r="L116" s="45">
         <f t="shared" si="15"/>
         <v>0.003375</v>
       </c>
@@ -10042,7 +10046,7 @@
         <f>PRODUCT($B$38,$C$40,$D$38,$E$38,$F$38)</f>
         <v>48</v>
       </c>
-      <c r="J117" s="19">
+      <c r="J117" s="45">
         <f t="shared" si="13"/>
         <v>1.5e-5</v>
       </c>
@@ -10050,7 +10054,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L117" s="19">
+      <c r="L117" s="45">
         <f t="shared" si="15"/>
         <v>0.0015</v>
       </c>
@@ -10084,7 +10088,7 @@
         <f>PRODUCT($B$38,$C$40,$D$38,$E$38,$F$40)</f>
         <v>72</v>
       </c>
-      <c r="J118" s="19">
+      <c r="J118" s="45">
         <f t="shared" si="13"/>
         <v>2.25e-5</v>
       </c>
@@ -10092,7 +10096,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L118" s="19">
+      <c r="L118" s="45">
         <f t="shared" si="15"/>
         <v>0.00225</v>
       </c>
@@ -10126,7 +10130,7 @@
         <f>PRODUCT($B$38,$C$40,$D$38,$E$40,$F$38)</f>
         <v>72</v>
       </c>
-      <c r="J119" s="19">
+      <c r="J119" s="45">
         <f t="shared" si="13"/>
         <v>2.25e-5</v>
       </c>
@@ -10134,7 +10138,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L119" s="19">
+      <c r="L119" s="45">
         <f t="shared" si="15"/>
         <v>0.00225</v>
       </c>
@@ -10168,7 +10172,7 @@
         <f>PRODUCT($B$38,$C$40,$D$38,$E$40,$F$40)</f>
         <v>108</v>
       </c>
-      <c r="J120" s="19">
+      <c r="J120" s="45">
         <f t="shared" si="13"/>
         <v>3.375e-5</v>
       </c>
@@ -10176,7 +10180,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L120" s="19">
+      <c r="L120" s="45">
         <f t="shared" si="15"/>
         <v>0.003375</v>
       </c>
@@ -10210,7 +10214,7 @@
         <f>PRODUCT($B$38,$C$40,$D$40,$E$38,$F$38)</f>
         <v>72</v>
       </c>
-      <c r="J121" s="19">
+      <c r="J121" s="45">
         <f t="shared" si="13"/>
         <v>2.25e-5</v>
       </c>
@@ -10218,7 +10222,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L121" s="19">
+      <c r="L121" s="45">
         <f t="shared" si="15"/>
         <v>0.00225</v>
       </c>
@@ -10252,7 +10256,7 @@
         <f>PRODUCT($B$38,$C$40,$D$40,$E$38,$F$40)</f>
         <v>108</v>
       </c>
-      <c r="J122" s="19">
+      <c r="J122" s="45">
         <f t="shared" si="13"/>
         <v>3.375e-5</v>
       </c>
@@ -10260,7 +10264,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L122" s="19">
+      <c r="L122" s="45">
         <f t="shared" si="15"/>
         <v>0.003375</v>
       </c>
@@ -10294,7 +10298,7 @@
         <f>PRODUCT($B$38,$C$40,$D$40,$E$40,$F$38)</f>
         <v>108</v>
       </c>
-      <c r="J123" s="19">
+      <c r="J123" s="45">
         <f t="shared" si="13"/>
         <v>3.375e-5</v>
       </c>
@@ -10302,7 +10306,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L123" s="19">
+      <c r="L123" s="45">
         <f t="shared" si="15"/>
         <v>0.003375</v>
       </c>
@@ -10336,7 +10340,7 @@
         <f>PRODUCT($B$38,$C$40,$D$40,$E$40,$F$40)</f>
         <v>162</v>
       </c>
-      <c r="J124" s="19">
+      <c r="J124" s="45">
         <f t="shared" si="13"/>
         <v>5.0625e-5</v>
       </c>
@@ -10344,7 +10348,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L124" s="19">
+      <c r="L124" s="45">
         <f t="shared" si="15"/>
         <v>0.0050625</v>
       </c>
@@ -10378,7 +10382,7 @@
         <f>PRODUCT($B$40,$C$38,$D$38,$E$38,$F$38)</f>
         <v>32</v>
       </c>
-      <c r="J125" s="19">
+      <c r="J125" s="45">
         <f t="shared" si="13"/>
         <v>1e-5</v>
       </c>
@@ -10386,7 +10390,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L125" s="19">
+      <c r="L125" s="45">
         <f t="shared" si="15"/>
         <v>0.001</v>
       </c>
@@ -10420,7 +10424,7 @@
         <f>PRODUCT($B$40,$C$38,$D$38,$E$38,$F$40)</f>
         <v>48</v>
       </c>
-      <c r="J126" s="19">
+      <c r="J126" s="45">
         <f t="shared" si="13"/>
         <v>1.5e-5</v>
       </c>
@@ -10428,7 +10432,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L126" s="19">
+      <c r="L126" s="45">
         <f t="shared" si="15"/>
         <v>0.0015</v>
       </c>
@@ -10462,7 +10466,7 @@
         <f>PRODUCT($B$40,$C$38,$D$38,$E$40,$F$38)</f>
         <v>48</v>
       </c>
-      <c r="J127" s="19">
+      <c r="J127" s="45">
         <f t="shared" si="13"/>
         <v>1.5e-5</v>
       </c>
@@ -10470,7 +10474,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L127" s="19">
+      <c r="L127" s="45">
         <f t="shared" si="15"/>
         <v>0.0015</v>
       </c>
@@ -10504,7 +10508,7 @@
         <f>PRODUCT($B$40,$C$38,$D$38,$E$40,$F$40)</f>
         <v>72</v>
       </c>
-      <c r="J128" s="19">
+      <c r="J128" s="45">
         <f t="shared" si="13"/>
         <v>2.25e-5</v>
       </c>
@@ -10512,7 +10516,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L128" s="19">
+      <c r="L128" s="45">
         <f t="shared" si="15"/>
         <v>0.00225</v>
       </c>
@@ -10546,7 +10550,7 @@
         <f>PRODUCT($B$40,$C$38,$D$40,$E$38,$F$38)</f>
         <v>48</v>
       </c>
-      <c r="J129" s="19">
+      <c r="J129" s="45">
         <f t="shared" si="13"/>
         <v>1.5e-5</v>
       </c>
@@ -10554,7 +10558,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L129" s="19">
+      <c r="L129" s="45">
         <f t="shared" si="15"/>
         <v>0.0015</v>
       </c>
@@ -10588,7 +10592,7 @@
         <f>PRODUCT($B$40,$C$38,$D$40,$E$38,$F$40)</f>
         <v>72</v>
       </c>
-      <c r="J130" s="19">
+      <c r="J130" s="45">
         <f t="shared" si="13"/>
         <v>2.25e-5</v>
       </c>
@@ -10596,7 +10600,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L130" s="19">
+      <c r="L130" s="45">
         <f t="shared" si="15"/>
         <v>0.00225</v>
       </c>
@@ -10630,7 +10634,7 @@
         <f>PRODUCT($B$40,$C$38,$D$40,$E$40,$F$38)</f>
         <v>72</v>
       </c>
-      <c r="J131" s="19">
+      <c r="J131" s="45">
         <f t="shared" si="13"/>
         <v>2.25e-5</v>
       </c>
@@ -10638,7 +10642,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L131" s="19">
+      <c r="L131" s="45">
         <f t="shared" si="15"/>
         <v>0.00225</v>
       </c>
@@ -10672,7 +10676,7 @@
         <f>PRODUCT($B$40,$C$38,$D$40,$E$40,$F$40)</f>
         <v>108</v>
       </c>
-      <c r="J132" s="19">
+      <c r="J132" s="45">
         <f t="shared" si="13"/>
         <v>3.375e-5</v>
       </c>
@@ -10680,7 +10684,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L132" s="19">
+      <c r="L132" s="45">
         <f t="shared" si="15"/>
         <v>0.003375</v>
       </c>
@@ -10714,7 +10718,7 @@
         <f>PRODUCT($B$40,$C$40,$D$38,$E$38,$F$38)</f>
         <v>48</v>
       </c>
-      <c r="J133" s="19">
+      <c r="J133" s="45">
         <f t="shared" si="13"/>
         <v>1.5e-5</v>
       </c>
@@ -10722,7 +10726,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L133" s="19">
+      <c r="L133" s="45">
         <f t="shared" si="15"/>
         <v>0.0015</v>
       </c>
@@ -10756,7 +10760,7 @@
         <f>PRODUCT($B$40,$C$40,$D$38,$E$38,$F$40)</f>
         <v>72</v>
       </c>
-      <c r="J134" s="19">
+      <c r="J134" s="45">
         <f t="shared" si="13"/>
         <v>2.25e-5</v>
       </c>
@@ -10764,7 +10768,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L134" s="19">
+      <c r="L134" s="45">
         <f t="shared" si="15"/>
         <v>0.00225</v>
       </c>
@@ -10798,7 +10802,7 @@
         <f>PRODUCT($B$40,$C$40,$D$38,$E$40,$F$38)</f>
         <v>72</v>
       </c>
-      <c r="J135" s="19">
+      <c r="J135" s="45">
         <f t="shared" si="13"/>
         <v>2.25e-5</v>
       </c>
@@ -10806,7 +10810,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L135" s="19">
+      <c r="L135" s="45">
         <f t="shared" si="15"/>
         <v>0.00225</v>
       </c>
@@ -10840,7 +10844,7 @@
         <f>PRODUCT($B$40,$C$40,$D$38,$E$40,$F$40)</f>
         <v>108</v>
       </c>
-      <c r="J136" s="19">
+      <c r="J136" s="45">
         <f t="shared" si="13"/>
         <v>3.375e-5</v>
       </c>
@@ -10848,7 +10852,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L136" s="19">
+      <c r="L136" s="45">
         <f t="shared" si="15"/>
         <v>0.003375</v>
       </c>
@@ -10882,7 +10886,7 @@
         <f>PRODUCT($B$40,$C$40,$D$40,$E$38,$F$38)</f>
         <v>72</v>
       </c>
-      <c r="J137" s="19">
+      <c r="J137" s="45">
         <f t="shared" si="13"/>
         <v>2.25e-5</v>
       </c>
@@ -10890,7 +10894,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L137" s="19">
+      <c r="L137" s="45">
         <f t="shared" si="15"/>
         <v>0.00225</v>
       </c>
@@ -10924,7 +10928,7 @@
         <f>PRODUCT($B$40,$C$40,$D$40,$E$38,$F$40)</f>
         <v>108</v>
       </c>
-      <c r="J138" s="19">
+      <c r="J138" s="45">
         <f t="shared" si="13"/>
         <v>3.375e-5</v>
       </c>
@@ -10932,7 +10936,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L138" s="19">
+      <c r="L138" s="45">
         <f t="shared" si="15"/>
         <v>0.003375</v>
       </c>
@@ -10966,7 +10970,7 @@
         <f>PRODUCT($B$40,$C$40,$D$40,$E$40,$F$38)</f>
         <v>108</v>
       </c>
-      <c r="J139" s="19">
+      <c r="J139" s="45">
         <f t="shared" si="13"/>
         <v>3.375e-5</v>
       </c>
@@ -10974,7 +10978,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="L139" s="19">
+      <c r="L139" s="45">
         <f t="shared" si="15"/>
         <v>0.003375</v>
       </c>
@@ -11008,7 +11012,7 @@
         <f>PRODUCT($B$38,$C$38,$D$40,$E$38,($F$45-$F$38-$F$40))</f>
         <v>360</v>
       </c>
-      <c r="J140" s="19">
+      <c r="J140" s="45">
         <f t="shared" si="13"/>
         <v>0.0001125</v>
       </c>
@@ -11016,7 +11020,7 @@
         <f t="shared" ref="K140:K152" si="16">MAX(0,INDEX($B$3:$D$7,MATCH($B140,$A$3:$A$7,0),MATCH($C140,$B$2:$D$2,0)))</f>
         <v>25</v>
       </c>
-      <c r="L140" s="19">
+      <c r="L140" s="45">
         <f t="shared" si="15"/>
         <v>0.0028125</v>
       </c>
@@ -11050,7 +11054,7 @@
         <f>PRODUCT($B$38,$C$38,$D$40,$E$40,($F$45-$F$38-$F$40))</f>
         <v>540</v>
       </c>
-      <c r="J141" s="19">
+      <c r="J141" s="45">
         <f t="shared" si="13"/>
         <v>0.00016875</v>
       </c>
@@ -11058,7 +11062,7 @@
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
-      <c r="L141" s="19">
+      <c r="L141" s="45">
         <f t="shared" si="15"/>
         <v>0.00421875</v>
       </c>
@@ -11092,7 +11096,7 @@
         <f>PRODUCT($B$38,$C$40,$D$38,$E$38,($F$45-$F$38-$F$40))</f>
         <v>360</v>
       </c>
-      <c r="J142" s="19">
+      <c r="J142" s="45">
         <f t="shared" si="13"/>
         <v>0.0001125</v>
       </c>
@@ -11100,7 +11104,7 @@
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
-      <c r="L142" s="19">
+      <c r="L142" s="45">
         <f t="shared" si="15"/>
         <v>0.0028125</v>
       </c>
@@ -11134,7 +11138,7 @@
         <f>PRODUCT($B$38,$C$40,$D$38,$E$40,($F$45-$F$38-$F$40))</f>
         <v>540</v>
       </c>
-      <c r="J143" s="19">
+      <c r="J143" s="45">
         <f t="shared" si="13"/>
         <v>0.00016875</v>
       </c>
@@ -11142,7 +11146,7 @@
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
-      <c r="L143" s="19">
+      <c r="L143" s="45">
         <f t="shared" si="15"/>
         <v>0.00421875</v>
       </c>
@@ -11176,7 +11180,7 @@
         <f>PRODUCT($B$38,$C$40,$D$40,$E$38,($F$45-$F$38-$F$40))</f>
         <v>540</v>
       </c>
-      <c r="J144" s="19">
+      <c r="J144" s="45">
         <f t="shared" si="13"/>
         <v>0.00016875</v>
       </c>
@@ -11184,7 +11188,7 @@
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
-      <c r="L144" s="19">
+      <c r="L144" s="45">
         <f t="shared" si="15"/>
         <v>0.00421875</v>
       </c>
@@ -11218,7 +11222,7 @@
         <f>PRODUCT($B$38,$C$40,$D$40,$E$40,($F$45-$F$38-$F$40))</f>
         <v>810</v>
       </c>
-      <c r="J145" s="19">
+      <c r="J145" s="45">
         <f t="shared" si="13"/>
         <v>0.000253125</v>
       </c>
@@ -11226,7 +11230,7 @@
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
-      <c r="L145" s="19">
+      <c r="L145" s="45">
         <f t="shared" si="15"/>
         <v>0.006328125</v>
       </c>
@@ -11260,7 +11264,7 @@
         <f>PRODUCT($B$40,$C$38,$D$38,$E$38,($F$45-$F$38-$F$40))</f>
         <v>240</v>
       </c>
-      <c r="J146" s="19">
+      <c r="J146" s="45">
         <f t="shared" si="13"/>
         <v>7.5e-5</v>
       </c>
@@ -11268,7 +11272,7 @@
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
-      <c r="L146" s="19">
+      <c r="L146" s="45">
         <f t="shared" si="15"/>
         <v>0.001875</v>
       </c>
@@ -11302,7 +11306,7 @@
         <f>PRODUCT($B$40,$C$38,$D$38,$E$40,($F$45-$F$38-$F$40))</f>
         <v>360</v>
       </c>
-      <c r="J147" s="19">
+      <c r="J147" s="45">
         <f t="shared" si="13"/>
         <v>0.0001125</v>
       </c>
@@ -11310,7 +11314,7 @@
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
-      <c r="L147" s="19">
+      <c r="L147" s="45">
         <f t="shared" si="15"/>
         <v>0.0028125</v>
       </c>
@@ -11344,7 +11348,7 @@
         <f>PRODUCT($B$40,$C$38,$D$40,$E$38,($F$45-$F$38-$F$40))</f>
         <v>360</v>
       </c>
-      <c r="J148" s="19">
+      <c r="J148" s="45">
         <f t="shared" si="13"/>
         <v>0.0001125</v>
       </c>
@@ -11352,7 +11356,7 @@
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
-      <c r="L148" s="19">
+      <c r="L148" s="45">
         <f t="shared" si="15"/>
         <v>0.0028125</v>
       </c>
@@ -11386,7 +11390,7 @@
         <f>PRODUCT($B$40,$C$38,$D$40,$E$40,($F$45-$F$38-$F$40))</f>
         <v>540</v>
       </c>
-      <c r="J149" s="19">
+      <c r="J149" s="45">
         <f t="shared" si="13"/>
         <v>0.00016875</v>
       </c>
@@ -11394,7 +11398,7 @@
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
-      <c r="L149" s="19">
+      <c r="L149" s="45">
         <f t="shared" si="15"/>
         <v>0.00421875</v>
       </c>
@@ -11428,7 +11432,7 @@
         <f>PRODUCT($B$40,$C$40,$D$38,$E$38,($F$45-$F$38-$F$40))</f>
         <v>360</v>
       </c>
-      <c r="J150" s="19">
+      <c r="J150" s="45">
         <f t="shared" si="13"/>
         <v>0.0001125</v>
       </c>
@@ -11436,7 +11440,7 @@
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
-      <c r="L150" s="19">
+      <c r="L150" s="45">
         <f t="shared" si="15"/>
         <v>0.0028125</v>
       </c>
@@ -11470,7 +11474,7 @@
         <f>PRODUCT($B$40,$C$40,$D$38,$E$40,($F$45-$F$38-$F$40))</f>
         <v>540</v>
       </c>
-      <c r="J151" s="19">
+      <c r="J151" s="45">
         <f t="shared" si="13"/>
         <v>0.00016875</v>
       </c>
@@ -11478,7 +11482,7 @@
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
-      <c r="L151" s="19">
+      <c r="L151" s="45">
         <f t="shared" si="15"/>
         <v>0.00421875</v>
       </c>
@@ -11512,7 +11516,7 @@
         <f>PRODUCT($B$40,$C$40,$D$40,$E$38,($F$45-$F$38-$F$40))</f>
         <v>540</v>
       </c>
-      <c r="J152" s="19">
+      <c r="J152" s="45">
         <f t="shared" si="13"/>
         <v>0.00016875</v>
       </c>
@@ -11520,7 +11524,7 @@
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
-      <c r="L152" s="19">
+      <c r="L152" s="45">
         <f t="shared" si="15"/>
         <v>0.00421875</v>
       </c>
@@ -11554,7 +11558,7 @@
         <f>PRODUCT($B$38,$C$38,$D$40,($E$45-$E$38-$E$40),$F$45)</f>
         <v>3600</v>
       </c>
-      <c r="J153" s="19">
+      <c r="J153" s="45">
         <f t="shared" si="13"/>
         <v>0.001125</v>
       </c>
@@ -11562,7 +11566,7 @@
         <f t="shared" ref="K153:K158" si="17">MAX(0,INDEX($B$3:$D$7,MATCH($B153,$A$3:$A$7,0),MATCH($C153,$B$2:$D$2,0)))</f>
         <v>5</v>
       </c>
-      <c r="L153" s="19">
+      <c r="L153" s="45">
         <f t="shared" si="15"/>
         <v>0.005625</v>
       </c>
@@ -11596,7 +11600,7 @@
         <f>PRODUCT($B$38,$C$40,$D$38,($E$45-$E$38-$E$40),$F$45)</f>
         <v>3600</v>
       </c>
-      <c r="J154" s="19">
+      <c r="J154" s="45">
         <f t="shared" si="13"/>
         <v>0.001125</v>
       </c>
@@ -11604,7 +11608,7 @@
         <f t="shared" si="17"/>
         <v>5</v>
       </c>
-      <c r="L154" s="19">
+      <c r="L154" s="45">
         <f t="shared" si="15"/>
         <v>0.005625</v>
       </c>
@@ -11638,7 +11642,7 @@
         <f>PRODUCT($B$38,$C$40,$D$40,($E$45-$E$38-$E$40),$F$45)</f>
         <v>5400</v>
       </c>
-      <c r="J155" s="19">
+      <c r="J155" s="45">
         <f t="shared" si="13"/>
         <v>0.0016875</v>
       </c>
@@ -11646,7 +11650,7 @@
         <f t="shared" si="17"/>
         <v>5</v>
       </c>
-      <c r="L155" s="19">
+      <c r="L155" s="45">
         <f t="shared" si="15"/>
         <v>0.0084375</v>
       </c>
@@ -11680,7 +11684,7 @@
         <f>PRODUCT($B$40,$C$38,$D$38,($E$45-$E$38-$E$40),$F$45)</f>
         <v>2400</v>
       </c>
-      <c r="J156" s="19">
+      <c r="J156" s="45">
         <f t="shared" si="13"/>
         <v>0.00075</v>
       </c>
@@ -11688,7 +11692,7 @@
         <f t="shared" si="17"/>
         <v>5</v>
       </c>
-      <c r="L156" s="19">
+      <c r="L156" s="45">
         <f t="shared" si="15"/>
         <v>0.00375</v>
       </c>
@@ -11722,7 +11726,7 @@
         <f>PRODUCT($B$40,$C$38,$D$40,($E$45-$E$38-$E$40),$F$45)</f>
         <v>3600</v>
       </c>
-      <c r="J157" s="19">
+      <c r="J157" s="45">
         <f t="shared" si="13"/>
         <v>0.001125</v>
       </c>
@@ -11730,7 +11734,7 @@
         <f t="shared" si="17"/>
         <v>5</v>
       </c>
-      <c r="L157" s="19">
+      <c r="L157" s="45">
         <f t="shared" si="15"/>
         <v>0.005625</v>
       </c>
@@ -11764,7 +11768,7 @@
         <f>PRODUCT($B$40,$C$40,$D$38,($E$45-$E$38-$E$40),$F$45)</f>
         <v>3600</v>
       </c>
-      <c r="J158" s="19">
+      <c r="J158" s="45">
         <f t="shared" si="13"/>
         <v>0.001125</v>
       </c>
@@ -11772,7 +11776,7 @@
         <f t="shared" si="17"/>
         <v>5</v>
       </c>
-      <c r="L158" s="19">
+      <c r="L158" s="45">
         <f t="shared" si="15"/>
         <v>0.005625</v>
       </c>
@@ -11806,7 +11810,7 @@
         <f>PRODUCT($B$38,$C$38,$D$41,$E$38,$F$38)</f>
         <v>64</v>
       </c>
-      <c r="J159" s="19">
+      <c r="J159" s="45">
         <f t="shared" si="13"/>
         <v>2e-5</v>
       </c>
@@ -11814,7 +11818,7 @@
         <f t="shared" ref="K159:K185" si="18">MAX(0,INDEX($B$3:$D$7,MATCH($B159,$A$3:$A$7,0),MATCH($C159,$B$2:$D$2,0)))</f>
         <v>75</v>
       </c>
-      <c r="L159" s="19">
+      <c r="L159" s="45">
         <f t="shared" si="15"/>
         <v>0.0015</v>
       </c>
@@ -11848,7 +11852,7 @@
         <f>PRODUCT($B$38,$C$38,$D$41,$E$38,$F$41)</f>
         <v>128</v>
       </c>
-      <c r="J160" s="19">
+      <c r="J160" s="45">
         <f t="shared" si="13"/>
         <v>4e-5</v>
       </c>
@@ -11856,7 +11860,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L160" s="19">
+      <c r="L160" s="45">
         <f t="shared" si="15"/>
         <v>0.003</v>
       </c>
@@ -11890,7 +11894,7 @@
         <f>PRODUCT($B$38,$C$38,$D$41,$E$41,$F$38)</f>
         <v>128</v>
       </c>
-      <c r="J161" s="19">
+      <c r="J161" s="45">
         <f t="shared" si="13"/>
         <v>4e-5</v>
       </c>
@@ -11898,7 +11902,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L161" s="19">
+      <c r="L161" s="45">
         <f t="shared" si="15"/>
         <v>0.003</v>
       </c>
@@ -11932,7 +11936,7 @@
         <f>PRODUCT($B$38,$C$38,$D$41,$E$41,$F$41)</f>
         <v>256</v>
       </c>
-      <c r="J162" s="19">
+      <c r="J162" s="45">
         <f t="shared" si="13"/>
         <v>8e-5</v>
       </c>
@@ -11940,7 +11944,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L162" s="19">
+      <c r="L162" s="45">
         <f t="shared" si="15"/>
         <v>0.006</v>
       </c>
@@ -11974,7 +11978,7 @@
         <f>PRODUCT($B$38,$C$41,$D$38,$E$38,$F$38)</f>
         <v>80</v>
       </c>
-      <c r="J163" s="19">
+      <c r="J163" s="45">
         <f t="shared" si="13"/>
         <v>2.5e-5</v>
       </c>
@@ -11982,7 +11986,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L163" s="19">
+      <c r="L163" s="45">
         <f t="shared" si="15"/>
         <v>0.001875</v>
       </c>
@@ -12016,7 +12020,7 @@
         <f>PRODUCT($B$38,$C$41,$D$38,$E$38,$F$41)</f>
         <v>160</v>
       </c>
-      <c r="J164" s="19">
+      <c r="J164" s="45">
         <f t="shared" si="13"/>
         <v>5e-5</v>
       </c>
@@ -12024,7 +12028,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L164" s="19">
+      <c r="L164" s="45">
         <f t="shared" si="15"/>
         <v>0.00375</v>
       </c>
@@ -12058,7 +12062,7 @@
         <f>PRODUCT($B$38,$C$41,$D$38,$E$41,$F$38)</f>
         <v>160</v>
       </c>
-      <c r="J165" s="19">
+      <c r="J165" s="45">
         <f t="shared" si="13"/>
         <v>5e-5</v>
       </c>
@@ -12066,7 +12070,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L165" s="19">
+      <c r="L165" s="45">
         <f t="shared" si="15"/>
         <v>0.00375</v>
       </c>
@@ -12100,7 +12104,7 @@
         <f>PRODUCT($B$38,$C$41,$D$38,$E$41,$F$41)</f>
         <v>320</v>
       </c>
-      <c r="J166" s="19">
+      <c r="J166" s="45">
         <f t="shared" si="13"/>
         <v>0.0001</v>
       </c>
@@ -12108,7 +12112,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L166" s="19">
+      <c r="L166" s="45">
         <f t="shared" si="15"/>
         <v>0.0075</v>
       </c>
@@ -12142,7 +12146,7 @@
         <f>PRODUCT($B$38,$C$41,$D$41,$E$38,$F$38)</f>
         <v>160</v>
       </c>
-      <c r="J167" s="19">
+      <c r="J167" s="45">
         <f t="shared" si="13"/>
         <v>5e-5</v>
       </c>
@@ -12150,7 +12154,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L167" s="19">
+      <c r="L167" s="45">
         <f t="shared" si="15"/>
         <v>0.00375</v>
       </c>
@@ -12184,7 +12188,7 @@
         <f>PRODUCT($B$38,$C$41,$D$41,$E$38,$F$41)</f>
         <v>320</v>
       </c>
-      <c r="J168" s="19">
+      <c r="J168" s="45">
         <f t="shared" si="13"/>
         <v>0.0001</v>
       </c>
@@ -12192,7 +12196,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L168" s="19">
+      <c r="L168" s="45">
         <f t="shared" si="15"/>
         <v>0.0075</v>
       </c>
@@ -12226,7 +12230,7 @@
         <f>PRODUCT($B$38,$C$41,$D$41,$E$41,$F$38)</f>
         <v>320</v>
       </c>
-      <c r="J169" s="19">
+      <c r="J169" s="45">
         <f t="shared" si="13"/>
         <v>0.0001</v>
       </c>
@@ -12234,7 +12238,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L169" s="19">
+      <c r="L169" s="45">
         <f t="shared" si="15"/>
         <v>0.0075</v>
       </c>
@@ -12268,7 +12272,7 @@
         <f>PRODUCT($B$38,$C$41,$D$41,$E$41,$F$41)</f>
         <v>640</v>
       </c>
-      <c r="J170" s="19">
+      <c r="J170" s="45">
         <f t="shared" si="13"/>
         <v>0.0002</v>
       </c>
@@ -12276,7 +12280,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L170" s="19">
+      <c r="L170" s="45">
         <f t="shared" si="15"/>
         <v>0.015</v>
       </c>
@@ -12310,7 +12314,7 @@
         <f>PRODUCT($B$41,$C$38,$D$38,$E$38,$F$38)</f>
         <v>64</v>
       </c>
-      <c r="J171" s="19">
+      <c r="J171" s="45">
         <f t="shared" si="13"/>
         <v>2e-5</v>
       </c>
@@ -12318,7 +12322,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L171" s="19">
+      <c r="L171" s="45">
         <f t="shared" si="15"/>
         <v>0.0015</v>
       </c>
@@ -12352,7 +12356,7 @@
         <f>PRODUCT($B$41,$C$38,$D$38,$E$38,$F$41)</f>
         <v>128</v>
       </c>
-      <c r="J172" s="19">
+      <c r="J172" s="45">
         <f t="shared" si="13"/>
         <v>4e-5</v>
       </c>
@@ -12360,7 +12364,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L172" s="19">
+      <c r="L172" s="45">
         <f t="shared" si="15"/>
         <v>0.003</v>
       </c>
@@ -12394,7 +12398,7 @@
         <f>PRODUCT($B$41,$C$38,$D$38,$E$41,$F$38)</f>
         <v>128</v>
       </c>
-      <c r="J173" s="19">
+      <c r="J173" s="45">
         <f t="shared" si="13"/>
         <v>4e-5</v>
       </c>
@@ -12402,7 +12406,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L173" s="19">
+      <c r="L173" s="45">
         <f t="shared" si="15"/>
         <v>0.003</v>
       </c>
@@ -12436,7 +12440,7 @@
         <f>PRODUCT($B$41,$C$38,$D$38,$E$41,$F$41)</f>
         <v>256</v>
       </c>
-      <c r="J174" s="19">
+      <c r="J174" s="45">
         <f t="shared" si="13"/>
         <v>8e-5</v>
       </c>
@@ -12444,7 +12448,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L174" s="19">
+      <c r="L174" s="45">
         <f t="shared" si="15"/>
         <v>0.006</v>
       </c>
@@ -12478,7 +12482,7 @@
         <f>PRODUCT($B$41,$C$38,$D$41,$E$38,$F$38)</f>
         <v>128</v>
       </c>
-      <c r="J175" s="19">
+      <c r="J175" s="45">
         <f t="shared" si="13"/>
         <v>4e-5</v>
       </c>
@@ -12486,7 +12490,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L175" s="19">
+      <c r="L175" s="45">
         <f t="shared" si="15"/>
         <v>0.003</v>
       </c>
@@ -12520,7 +12524,7 @@
         <f>PRODUCT($B$41,$C$38,$D$41,$E$38,$F$41)</f>
         <v>256</v>
       </c>
-      <c r="J176" s="19">
+      <c r="J176" s="45">
         <f t="shared" si="13"/>
         <v>8e-5</v>
       </c>
@@ -12528,7 +12532,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L176" s="19">
+      <c r="L176" s="45">
         <f t="shared" si="15"/>
         <v>0.006</v>
       </c>
@@ -12562,7 +12566,7 @@
         <f>PRODUCT($B$41,$C$38,$D$41,$E$41,$F$38)</f>
         <v>256</v>
       </c>
-      <c r="J177" s="19">
+      <c r="J177" s="45">
         <f t="shared" ref="J177:J185" si="19">I177/$B$48</f>
         <v>8e-5</v>
       </c>
@@ -12570,7 +12574,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L177" s="19">
+      <c r="L177" s="45">
         <f t="shared" ref="L177:L185" si="20">J177*K177</f>
         <v>0.006</v>
       </c>
@@ -12604,7 +12608,7 @@
         <f>PRODUCT($B$41,$C$38,$D$41,$E$41,$F$41)</f>
         <v>512</v>
       </c>
-      <c r="J178" s="19">
+      <c r="J178" s="45">
         <f t="shared" si="19"/>
         <v>0.00016</v>
       </c>
@@ -12612,7 +12616,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L178" s="19">
+      <c r="L178" s="45">
         <f t="shared" si="20"/>
         <v>0.012</v>
       </c>
@@ -12646,7 +12650,7 @@
         <f>PRODUCT($B$41,$C$41,$D$38,$E$38,$F$38)</f>
         <v>160</v>
       </c>
-      <c r="J179" s="19">
+      <c r="J179" s="45">
         <f t="shared" si="19"/>
         <v>5e-5</v>
       </c>
@@ -12654,7 +12658,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L179" s="19">
+      <c r="L179" s="45">
         <f t="shared" si="20"/>
         <v>0.00375</v>
       </c>
@@ -12688,7 +12692,7 @@
         <f>PRODUCT($B$41,$C$41,$D$38,$E$38,$F$41)</f>
         <v>320</v>
       </c>
-      <c r="J180" s="19">
+      <c r="J180" s="45">
         <f t="shared" si="19"/>
         <v>0.0001</v>
       </c>
@@ -12696,7 +12700,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L180" s="19">
+      <c r="L180" s="45">
         <f t="shared" si="20"/>
         <v>0.0075</v>
       </c>
@@ -12730,7 +12734,7 @@
         <f>PRODUCT($B$41,$C$41,$D$38,$E$41,$F$38)</f>
         <v>320</v>
       </c>
-      <c r="J181" s="19">
+      <c r="J181" s="45">
         <f t="shared" si="19"/>
         <v>0.0001</v>
       </c>
@@ -12738,7 +12742,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L181" s="19">
+      <c r="L181" s="45">
         <f t="shared" si="20"/>
         <v>0.0075</v>
       </c>
@@ -12772,7 +12776,7 @@
         <f>PRODUCT($B$41,$C$41,$D$38,$E$41,$F$41)</f>
         <v>640</v>
       </c>
-      <c r="J182" s="19">
+      <c r="J182" s="45">
         <f t="shared" si="19"/>
         <v>0.0002</v>
       </c>
@@ -12780,7 +12784,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L182" s="19">
+      <c r="L182" s="45">
         <f t="shared" si="20"/>
         <v>0.015</v>
       </c>
@@ -12814,7 +12818,7 @@
         <f>PRODUCT($B$41,$C$41,$D$41,$E$38,$F$38)</f>
         <v>320</v>
       </c>
-      <c r="J183" s="19">
+      <c r="J183" s="45">
         <f t="shared" si="19"/>
         <v>0.0001</v>
       </c>
@@ -12822,7 +12826,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L183" s="19">
+      <c r="L183" s="45">
         <f t="shared" si="20"/>
         <v>0.0075</v>
       </c>
@@ -12856,7 +12860,7 @@
         <f>PRODUCT($B$41,$C$41,$D$41,$E$38,$F$41)</f>
         <v>640</v>
       </c>
-      <c r="J184" s="19">
+      <c r="J184" s="45">
         <f t="shared" si="19"/>
         <v>0.0002</v>
       </c>
@@ -12864,7 +12868,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L184" s="19">
+      <c r="L184" s="45">
         <f t="shared" si="20"/>
         <v>0.015</v>
       </c>
@@ -12898,7 +12902,7 @@
         <f>PRODUCT($B$41,$C$41,$D$41,$E$41,$F$38)</f>
         <v>640</v>
       </c>
-      <c r="J185" s="19">
+      <c r="J185" s="45">
         <f t="shared" si="19"/>
         <v>0.0002</v>
       </c>
@@ -12906,7 +12910,7 @@
         <f t="shared" si="18"/>
         <v>75</v>
       </c>
-      <c r="L185" s="19">
+      <c r="L185" s="45">
         <f t="shared" si="20"/>
         <v>0.015</v>
       </c>
@@ -12940,7 +12944,7 @@
         <f>PRODUCT($B$38,$C$38,$D$41,$E$38,($F$45-$F$38-$F$41))</f>
         <v>448</v>
       </c>
-      <c r="J186" s="19">
+      <c r="J186" s="45">
         <f t="shared" ref="J186:J244" si="21">I186/$B$48</f>
         <v>0.00014</v>
       </c>
@@ -12948,7 +12952,7 @@
         <f t="shared" ref="K186:K198" si="22">MAX(0,INDEX($B$3:$D$7,MATCH($B186,$A$3:$A$7,0),MATCH($C186,$B$2:$D$2,0)))</f>
         <v>20</v>
       </c>
-      <c r="L186" s="19">
+      <c r="L186" s="45">
         <f t="shared" ref="L186:L244" si="23">J186*K186</f>
         <v>0.0028</v>
       </c>
@@ -12982,7 +12986,7 @@
         <f>PRODUCT($B$38,$C$38,$D$41,$E$41,($F$45-$F$38-$F$41))</f>
         <v>896</v>
       </c>
-      <c r="J187" s="19">
+      <c r="J187" s="45">
         <f t="shared" si="21"/>
         <v>0.00028</v>
       </c>
@@ -12990,7 +12994,7 @@
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
-      <c r="L187" s="19">
+      <c r="L187" s="45">
         <f t="shared" si="23"/>
         <v>0.0056</v>
       </c>
@@ -13024,7 +13028,7 @@
         <f>PRODUCT($B$38,$C$41,$D$38,$E$38,($F$45-$F$38-$F$41))</f>
         <v>560</v>
       </c>
-      <c r="J188" s="19">
+      <c r="J188" s="45">
         <f t="shared" si="21"/>
         <v>0.000175</v>
       </c>
@@ -13032,7 +13036,7 @@
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
-      <c r="L188" s="19">
+      <c r="L188" s="45">
         <f t="shared" si="23"/>
         <v>0.0035</v>
       </c>
@@ -13066,7 +13070,7 @@
         <f>PRODUCT($B$38,$C$41,$D$38,$E$41,($F$45-$F$38-$F$41))</f>
         <v>1120</v>
       </c>
-      <c r="J189" s="19">
+      <c r="J189" s="45">
         <f t="shared" si="21"/>
         <v>0.00035</v>
       </c>
@@ -13074,7 +13078,7 @@
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
-      <c r="L189" s="19">
+      <c r="L189" s="45">
         <f t="shared" si="23"/>
         <v>0.007</v>
       </c>
@@ -13108,7 +13112,7 @@
         <f>PRODUCT($B$38,$C$41,$D$41,$E$38,($F$45-$F$38-$F$41))</f>
         <v>1120</v>
       </c>
-      <c r="J190" s="19">
+      <c r="J190" s="45">
         <f t="shared" si="21"/>
         <v>0.00035</v>
       </c>
@@ -13116,7 +13120,7 @@
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
-      <c r="L190" s="19">
+      <c r="L190" s="45">
         <f t="shared" si="23"/>
         <v>0.007</v>
       </c>
@@ -13150,7 +13154,7 @@
         <f>PRODUCT($B$38,$C$41,$D$41,$E$41,($F$45-$F$38-$F$41))</f>
         <v>2240</v>
       </c>
-      <c r="J191" s="19">
+      <c r="J191" s="45">
         <f t="shared" si="21"/>
         <v>0.0007</v>
       </c>
@@ -13158,7 +13162,7 @@
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
-      <c r="L191" s="19">
+      <c r="L191" s="45">
         <f t="shared" si="23"/>
         <v>0.014</v>
       </c>
@@ -13192,7 +13196,7 @@
         <f>PRODUCT($B$41,$C$38,$D$38,$E$38,($F$45-$F$38-$F$41))</f>
         <v>448</v>
       </c>
-      <c r="J192" s="19">
+      <c r="J192" s="45">
         <f t="shared" si="21"/>
         <v>0.00014</v>
       </c>
@@ -13200,7 +13204,7 @@
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
-      <c r="L192" s="19">
+      <c r="L192" s="45">
         <f t="shared" si="23"/>
         <v>0.0028</v>
       </c>
@@ -13234,7 +13238,7 @@
         <f>PRODUCT($B$41,$C$38,$D$38,$E$41,($F$45-$F$38-$F$41))</f>
         <v>896</v>
       </c>
-      <c r="J193" s="19">
+      <c r="J193" s="45">
         <f t="shared" si="21"/>
         <v>0.00028</v>
       </c>
@@ -13242,7 +13246,7 @@
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
-      <c r="L193" s="19">
+      <c r="L193" s="45">
         <f t="shared" si="23"/>
         <v>0.0056</v>
       </c>
@@ -13276,7 +13280,7 @@
         <f>PRODUCT($B$41,$C$38,$D$41,$E$38,($F$45-$F$38-$F$41))</f>
         <v>896</v>
       </c>
-      <c r="J194" s="19">
+      <c r="J194" s="45">
         <f t="shared" si="21"/>
         <v>0.00028</v>
       </c>
@@ -13284,7 +13288,7 @@
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
-      <c r="L194" s="19">
+      <c r="L194" s="45">
         <f t="shared" si="23"/>
         <v>0.0056</v>
       </c>
@@ -13318,7 +13322,7 @@
         <f>PRODUCT($B$41,$C$38,$D$41,$E$41,($F$45-$F$38-$F$41))</f>
         <v>1792</v>
       </c>
-      <c r="J195" s="19">
+      <c r="J195" s="45">
         <f t="shared" si="21"/>
         <v>0.00056</v>
       </c>
@@ -13326,7 +13330,7 @@
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
-      <c r="L195" s="19">
+      <c r="L195" s="45">
         <f t="shared" si="23"/>
         <v>0.0112</v>
       </c>
@@ -13360,7 +13364,7 @@
         <f>PRODUCT($B$41,$C$41,$D$38,$E$38,($F$45-$F$38-$F$41))</f>
         <v>1120</v>
       </c>
-      <c r="J196" s="19">
+      <c r="J196" s="45">
         <f t="shared" si="21"/>
         <v>0.00035</v>
       </c>
@@ -13368,7 +13372,7 @@
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
-      <c r="L196" s="19">
+      <c r="L196" s="45">
         <f t="shared" si="23"/>
         <v>0.007</v>
       </c>
@@ -13402,7 +13406,7 @@
         <f>PRODUCT($B$41,$C$41,$D$38,$E$41,($F$45-$F$38-$F$41))</f>
         <v>2240</v>
       </c>
-      <c r="J197" s="19">
+      <c r="J197" s="45">
         <f t="shared" si="21"/>
         <v>0.0007</v>
       </c>
@@ -13410,7 +13414,7 @@
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
-      <c r="L197" s="19">
+      <c r="L197" s="45">
         <f t="shared" si="23"/>
         <v>0.014</v>
       </c>
@@ -13444,7 +13448,7 @@
         <f>PRODUCT($B$41,$C$41,$D$41,$E$38,($F$45-$F$38-$F$41))</f>
         <v>2240</v>
       </c>
-      <c r="J198" s="19">
+      <c r="J198" s="45">
         <f t="shared" si="21"/>
         <v>0.0007</v>
       </c>
@@ -13452,7 +13456,7 @@
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
-      <c r="L198" s="19">
+      <c r="L198" s="45">
         <f t="shared" si="23"/>
         <v>0.014</v>
       </c>
@@ -13486,7 +13490,7 @@
         <f>PRODUCT($B$38,$C$38,$D$41,($E$45-$E$38-$E$41),$F$45)</f>
         <v>4480</v>
       </c>
-      <c r="J199" s="19">
+      <c r="J199" s="45">
         <f t="shared" si="21"/>
         <v>0.0014</v>
       </c>
@@ -13494,7 +13498,7 @@
         <f t="shared" ref="K199:K204" si="24">MAX(0,INDEX($B$3:$D$7,MATCH($B199,$A$3:$A$7,0),MATCH($C199,$B$2:$D$2,0)))</f>
         <v>5</v>
       </c>
-      <c r="L199" s="19">
+      <c r="L199" s="45">
         <f t="shared" si="23"/>
         <v>0.007</v>
       </c>
@@ -13528,7 +13532,7 @@
         <f>PRODUCT($B$38,$C$41,$D$38,($E$45-$E$38-$E$41),$F$45)</f>
         <v>5600</v>
       </c>
-      <c r="J200" s="19">
+      <c r="J200" s="45">
         <f t="shared" si="21"/>
         <v>0.00175</v>
       </c>
@@ -13536,7 +13540,7 @@
         <f t="shared" si="24"/>
         <v>5</v>
       </c>
-      <c r="L200" s="19">
+      <c r="L200" s="45">
         <f t="shared" si="23"/>
         <v>0.00875</v>
       </c>
@@ -13570,7 +13574,7 @@
         <f>PRODUCT($B$38,$C$41,$D$41,($E$45-$E$38-$E$41),$F$45)</f>
         <v>11200</v>
       </c>
-      <c r="J201" s="19">
+      <c r="J201" s="45">
         <f t="shared" si="21"/>
         <v>0.0035</v>
       </c>
@@ -13578,7 +13582,7 @@
         <f t="shared" si="24"/>
         <v>5</v>
       </c>
-      <c r="L201" s="19">
+      <c r="L201" s="45">
         <f t="shared" si="23"/>
         <v>0.0175</v>
       </c>
@@ -13612,7 +13616,7 @@
         <f>PRODUCT($B$41,$C$38,$D$38,($E$45-$E$38-$E$41),$F$45)</f>
         <v>4480</v>
       </c>
-      <c r="J202" s="19">
+      <c r="J202" s="45">
         <f t="shared" si="21"/>
         <v>0.0014</v>
       </c>
@@ -13620,7 +13624,7 @@
         <f t="shared" si="24"/>
         <v>5</v>
       </c>
-      <c r="L202" s="19">
+      <c r="L202" s="45">
         <f t="shared" si="23"/>
         <v>0.007</v>
       </c>
@@ -13654,7 +13658,7 @@
         <f>PRODUCT($B$41,$C$38,$D$41,($E$45-$E$38-$E$41),$F$45)</f>
         <v>8960</v>
       </c>
-      <c r="J203" s="19">
+      <c r="J203" s="45">
         <f t="shared" si="21"/>
         <v>0.0028</v>
       </c>
@@ -13662,7 +13666,7 @@
         <f t="shared" si="24"/>
         <v>5</v>
       </c>
-      <c r="L203" s="19">
+      <c r="L203" s="45">
         <f t="shared" si="23"/>
         <v>0.014</v>
       </c>
@@ -13696,7 +13700,7 @@
         <f>PRODUCT($B$41,$C$41,$D$38,($E$45-$E$38-$E$41),$F$45)</f>
         <v>11200</v>
       </c>
-      <c r="J204" s="19">
+      <c r="J204" s="45">
         <f t="shared" si="21"/>
         <v>0.0035</v>
       </c>
@@ -13704,7 +13708,7 @@
         <f t="shared" si="24"/>
         <v>5</v>
       </c>
-      <c r="L204" s="19">
+      <c r="L204" s="45">
         <f t="shared" si="23"/>
         <v>0.0175</v>
       </c>
@@ -13738,7 +13742,7 @@
         <f>PRODUCT($B$38,$C$38,$D$42,$E$38,$F$38)</f>
         <v>64</v>
       </c>
-      <c r="J205" s="19">
+      <c r="J205" s="45">
         <f t="shared" si="21"/>
         <v>2e-5</v>
       </c>
@@ -13746,7 +13750,7 @@
         <f t="shared" ref="K205:K231" si="25">MAX(0,INDEX($B$3:$D$7,MATCH($B205,$A$3:$A$7,0),MATCH($C205,$B$2:$D$2,0)))</f>
         <v>75</v>
       </c>
-      <c r="L205" s="19">
+      <c r="L205" s="45">
         <f t="shared" si="23"/>
         <v>0.0015</v>
       </c>
@@ -13780,7 +13784,7 @@
         <f>PRODUCT($B$38,$C$38,$D$42,$E$38,$F$42)</f>
         <v>128</v>
       </c>
-      <c r="J206" s="19">
+      <c r="J206" s="45">
         <f t="shared" si="21"/>
         <v>4e-5</v>
       </c>
@@ -13788,7 +13792,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L206" s="19">
+      <c r="L206" s="45">
         <f t="shared" si="23"/>
         <v>0.003</v>
       </c>
@@ -13822,7 +13826,7 @@
         <f>PRODUCT($B$38,$C$38,$D$42,$E$42,$F$38)</f>
         <v>128</v>
       </c>
-      <c r="J207" s="19">
+      <c r="J207" s="45">
         <f t="shared" si="21"/>
         <v>4e-5</v>
       </c>
@@ -13830,7 +13834,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L207" s="19">
+      <c r="L207" s="45">
         <f t="shared" si="23"/>
         <v>0.003</v>
       </c>
@@ -13864,7 +13868,7 @@
         <f>PRODUCT($B$38,$C$38,$D$42,$E$42,$F$42)</f>
         <v>256</v>
       </c>
-      <c r="J208" s="19">
+      <c r="J208" s="45">
         <f t="shared" si="21"/>
         <v>8e-5</v>
       </c>
@@ -13872,7 +13876,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L208" s="19">
+      <c r="L208" s="45">
         <f t="shared" si="23"/>
         <v>0.006</v>
       </c>
@@ -13906,7 +13910,7 @@
         <f>PRODUCT($B$38,$C$42,$D$38,$E$38,$F$38)</f>
         <v>48</v>
       </c>
-      <c r="J209" s="19">
+      <c r="J209" s="45">
         <f t="shared" si="21"/>
         <v>1.5e-5</v>
       </c>
@@ -13914,7 +13918,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L209" s="19">
+      <c r="L209" s="45">
         <f t="shared" si="23"/>
         <v>0.001125</v>
       </c>
@@ -13948,7 +13952,7 @@
         <f>PRODUCT($B$38,$C$42,$D$38,$E$38,$F$42)</f>
         <v>96</v>
       </c>
-      <c r="J210" s="19">
+      <c r="J210" s="45">
         <f t="shared" si="21"/>
         <v>3e-5</v>
       </c>
@@ -13956,7 +13960,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L210" s="19">
+      <c r="L210" s="45">
         <f t="shared" si="23"/>
         <v>0.00225</v>
       </c>
@@ -13990,7 +13994,7 @@
         <f>PRODUCT($B$38,$C$42,$D$38,$E$42,$F$38)</f>
         <v>96</v>
       </c>
-      <c r="J211" s="19">
+      <c r="J211" s="45">
         <f t="shared" si="21"/>
         <v>3e-5</v>
       </c>
@@ -13998,7 +14002,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L211" s="19">
+      <c r="L211" s="45">
         <f t="shared" si="23"/>
         <v>0.00225</v>
       </c>
@@ -14032,7 +14036,7 @@
         <f>PRODUCT($B$38,$C$42,$D$38,$E$42,$F$42)</f>
         <v>192</v>
       </c>
-      <c r="J212" s="19">
+      <c r="J212" s="45">
         <f t="shared" si="21"/>
         <v>6e-5</v>
       </c>
@@ -14040,7 +14044,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L212" s="19">
+      <c r="L212" s="45">
         <f t="shared" si="23"/>
         <v>0.0045</v>
       </c>
@@ -14074,7 +14078,7 @@
         <f>PRODUCT($B$38,$C$42,$D$42,$E$38,$F$38)</f>
         <v>96</v>
       </c>
-      <c r="J213" s="19">
+      <c r="J213" s="45">
         <f t="shared" si="21"/>
         <v>3e-5</v>
       </c>
@@ -14082,7 +14086,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L213" s="19">
+      <c r="L213" s="45">
         <f t="shared" si="23"/>
         <v>0.00225</v>
       </c>
@@ -14116,7 +14120,7 @@
         <f>PRODUCT($B$38,$C$42,$D$42,$E$38,$F$42)</f>
         <v>192</v>
       </c>
-      <c r="J214" s="19">
+      <c r="J214" s="45">
         <f t="shared" si="21"/>
         <v>6e-5</v>
       </c>
@@ -14124,7 +14128,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L214" s="19">
+      <c r="L214" s="45">
         <f t="shared" si="23"/>
         <v>0.0045</v>
       </c>
@@ -14158,7 +14162,7 @@
         <f>PRODUCT($B$38,$C$42,$D$42,$E$42,$F$38)</f>
         <v>192</v>
       </c>
-      <c r="J215" s="19">
+      <c r="J215" s="45">
         <f t="shared" si="21"/>
         <v>6e-5</v>
       </c>
@@ -14166,7 +14170,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L215" s="19">
+      <c r="L215" s="45">
         <f t="shared" si="23"/>
         <v>0.0045</v>
       </c>
@@ -14200,7 +14204,7 @@
         <f>PRODUCT($B$38,$C$42,$D$42,$E$42,$F$42)</f>
         <v>384</v>
       </c>
-      <c r="J216" s="19">
+      <c r="J216" s="45">
         <f t="shared" si="21"/>
         <v>0.00012</v>
       </c>
@@ -14208,7 +14212,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L216" s="19">
+      <c r="L216" s="45">
         <f t="shared" si="23"/>
         <v>0.009</v>
       </c>
@@ -14242,7 +14246,7 @@
         <f>PRODUCT($B$42,$C$38,$D$38,$E$38,$F$38)</f>
         <v>80</v>
       </c>
-      <c r="J217" s="19">
+      <c r="J217" s="45">
         <f t="shared" si="21"/>
         <v>2.5e-5</v>
       </c>
@@ -14250,7 +14254,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L217" s="19">
+      <c r="L217" s="45">
         <f t="shared" si="23"/>
         <v>0.001875</v>
       </c>
@@ -14284,7 +14288,7 @@
         <f>PRODUCT($B$42,$C$38,$D$38,$E$38,$F$42)</f>
         <v>160</v>
       </c>
-      <c r="J218" s="19">
+      <c r="J218" s="45">
         <f t="shared" si="21"/>
         <v>5e-5</v>
       </c>
@@ -14292,7 +14296,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L218" s="19">
+      <c r="L218" s="45">
         <f t="shared" si="23"/>
         <v>0.00375</v>
       </c>
@@ -14326,7 +14330,7 @@
         <f>PRODUCT($B$42,$C$38,$D$38,$E$42,$F$38)</f>
         <v>160</v>
       </c>
-      <c r="J219" s="19">
+      <c r="J219" s="45">
         <f t="shared" si="21"/>
         <v>5e-5</v>
       </c>
@@ -14334,7 +14338,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L219" s="19">
+      <c r="L219" s="45">
         <f t="shared" si="23"/>
         <v>0.00375</v>
       </c>
@@ -14368,7 +14372,7 @@
         <f>PRODUCT($B$42,$C$38,$D$38,$E$42,$F$42)</f>
         <v>320</v>
       </c>
-      <c r="J220" s="19">
+      <c r="J220" s="45">
         <f t="shared" si="21"/>
         <v>0.0001</v>
       </c>
@@ -14376,7 +14380,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L220" s="19">
+      <c r="L220" s="45">
         <f t="shared" si="23"/>
         <v>0.0075</v>
       </c>
@@ -14410,7 +14414,7 @@
         <f>PRODUCT($B$42,$C$38,$D$42,$E$38,$F$38)</f>
         <v>160</v>
       </c>
-      <c r="J221" s="19">
+      <c r="J221" s="45">
         <f t="shared" si="21"/>
         <v>5e-5</v>
       </c>
@@ -14418,7 +14422,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L221" s="19">
+      <c r="L221" s="45">
         <f t="shared" si="23"/>
         <v>0.00375</v>
       </c>
@@ -14452,7 +14456,7 @@
         <f>PRODUCT($B$42,$C$38,$D$42,$E$38,$F$42)</f>
         <v>320</v>
       </c>
-      <c r="J222" s="19">
+      <c r="J222" s="45">
         <f t="shared" si="21"/>
         <v>0.0001</v>
       </c>
@@ -14460,7 +14464,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L222" s="19">
+      <c r="L222" s="45">
         <f t="shared" si="23"/>
         <v>0.0075</v>
       </c>
@@ -14494,7 +14498,7 @@
         <f>PRODUCT($B$42,$C$38,$D$42,$E$42,$F$38)</f>
         <v>320</v>
       </c>
-      <c r="J223" s="19">
+      <c r="J223" s="45">
         <f t="shared" si="21"/>
         <v>0.0001</v>
       </c>
@@ -14502,7 +14506,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L223" s="19">
+      <c r="L223" s="45">
         <f t="shared" si="23"/>
         <v>0.0075</v>
       </c>
@@ -14536,7 +14540,7 @@
         <f>PRODUCT($B$42,$C$38,$D$42,$E$42,$F$42)</f>
         <v>640</v>
       </c>
-      <c r="J224" s="19">
+      <c r="J224" s="45">
         <f t="shared" si="21"/>
         <v>0.0002</v>
       </c>
@@ -14544,7 +14548,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L224" s="19">
+      <c r="L224" s="45">
         <f t="shared" si="23"/>
         <v>0.015</v>
       </c>
@@ -14578,7 +14582,7 @@
         <f>PRODUCT($B$42,$C$42,$D$38,$E$38,$F$38)</f>
         <v>120</v>
       </c>
-      <c r="J225" s="19">
+      <c r="J225" s="45">
         <f t="shared" si="21"/>
         <v>3.75e-5</v>
       </c>
@@ -14586,7 +14590,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L225" s="19">
+      <c r="L225" s="45">
         <f t="shared" si="23"/>
         <v>0.0028125</v>
       </c>
@@ -14620,7 +14624,7 @@
         <f>PRODUCT($B$42,$C$42,$D$38,$E$38,$F$42)</f>
         <v>240</v>
       </c>
-      <c r="J226" s="19">
+      <c r="J226" s="45">
         <f t="shared" si="21"/>
         <v>7.5e-5</v>
       </c>
@@ -14628,7 +14632,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L226" s="19">
+      <c r="L226" s="45">
         <f t="shared" si="23"/>
         <v>0.005625</v>
       </c>
@@ -14662,7 +14666,7 @@
         <f>PRODUCT($B$42,$C$42,$D$38,$E$42,$F$38)</f>
         <v>240</v>
       </c>
-      <c r="J227" s="19">
+      <c r="J227" s="45">
         <f t="shared" si="21"/>
         <v>7.5e-5</v>
       </c>
@@ -14670,7 +14674,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L227" s="19">
+      <c r="L227" s="45">
         <f t="shared" si="23"/>
         <v>0.005625</v>
       </c>
@@ -14704,7 +14708,7 @@
         <f>PRODUCT($B$42,$C$42,$D$38,$E$42,$F$42)</f>
         <v>480</v>
       </c>
-      <c r="J228" s="19">
+      <c r="J228" s="45">
         <f t="shared" si="21"/>
         <v>0.00015</v>
       </c>
@@ -14712,7 +14716,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L228" s="19">
+      <c r="L228" s="45">
         <f t="shared" si="23"/>
         <v>0.01125</v>
       </c>
@@ -14746,7 +14750,7 @@
         <f>PRODUCT($B$42,$C$42,$D$42,$E$38,$F$38)</f>
         <v>240</v>
       </c>
-      <c r="J229" s="19">
+      <c r="J229" s="45">
         <f t="shared" si="21"/>
         <v>7.5e-5</v>
       </c>
@@ -14754,7 +14758,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L229" s="19">
+      <c r="L229" s="45">
         <f t="shared" si="23"/>
         <v>0.005625</v>
       </c>
@@ -14788,7 +14792,7 @@
         <f>PRODUCT($B$42,$C$42,$D$42,$E$38,$F$42)</f>
         <v>480</v>
       </c>
-      <c r="J230" s="19">
+      <c r="J230" s="45">
         <f t="shared" si="21"/>
         <v>0.00015</v>
       </c>
@@ -14796,7 +14800,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L230" s="19">
+      <c r="L230" s="45">
         <f t="shared" si="23"/>
         <v>0.01125</v>
       </c>
@@ -14830,7 +14834,7 @@
         <f>PRODUCT($B$42,$C$42,$D$42,$E$42,$F$38)</f>
         <v>480</v>
       </c>
-      <c r="J231" s="19">
+      <c r="J231" s="45">
         <f t="shared" si="21"/>
         <v>0.00015</v>
       </c>
@@ -14838,7 +14842,7 @@
         <f t="shared" si="25"/>
         <v>75</v>
       </c>
-      <c r="L231" s="19">
+      <c r="L231" s="45">
         <f t="shared" si="23"/>
         <v>0.01125</v>
       </c>
@@ -14872,7 +14876,7 @@
         <f>PRODUCT($B$38,$C$38,$D$42,$E$38,($F$45-$F$38-$F$42))</f>
         <v>448</v>
       </c>
-      <c r="J232" s="19">
+      <c r="J232" s="45">
         <f t="shared" si="21"/>
         <v>0.00014</v>
       </c>
@@ -14880,7 +14884,7 @@
         <f t="shared" ref="K232:K244" si="26">MAX(0,INDEX($B$3:$D$7,MATCH($B232,$A$3:$A$7,0),MATCH($C232,$B$2:$D$2,0)))</f>
         <v>20</v>
       </c>
-      <c r="L232" s="19">
+      <c r="L232" s="45">
         <f t="shared" si="23"/>
         <v>0.0028</v>
       </c>
@@ -14914,7 +14918,7 @@
         <f>PRODUCT($B$38,$C$38,$D$42,$E$42,($F$45-$F$38-$F$42))</f>
         <v>896</v>
       </c>
-      <c r="J233" s="19">
+      <c r="J233" s="45">
         <f t="shared" si="21"/>
         <v>0.00028</v>
       </c>
@@ -14922,7 +14926,7 @@
         <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="L233" s="19">
+      <c r="L233" s="45">
         <f t="shared" si="23"/>
         <v>0.0056</v>
       </c>
@@ -14956,7 +14960,7 @@
         <f>PRODUCT($B$38,$C$42,$D$38,$E$38,($F$45-$F$38-$F$42))</f>
         <v>336</v>
       </c>
-      <c r="J234" s="19">
+      <c r="J234" s="45">
         <f t="shared" si="21"/>
         <v>0.000105</v>
       </c>
@@ -14964,7 +14968,7 @@
         <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="L234" s="19">
+      <c r="L234" s="45">
         <f t="shared" si="23"/>
         <v>0.0021</v>
       </c>
@@ -14998,7 +15002,7 @@
         <f>PRODUCT($B$38,$C$42,$D$38,$E$42,($F$45-$F$38-$F$42))</f>
         <v>672</v>
       </c>
-      <c r="J235" s="19">
+      <c r="J235" s="45">
         <f t="shared" si="21"/>
         <v>0.00021</v>
       </c>
@@ -15006,7 +15010,7 @@
         <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="L235" s="19">
+      <c r="L235" s="45">
         <f t="shared" si="23"/>
         <v>0.0042</v>
       </c>
@@ -15040,7 +15044,7 @@
         <f>PRODUCT($B$38,$C$42,$D$42,$E$38,($F$45-$F$38-$F$42))</f>
         <v>672</v>
       </c>
-      <c r="J236" s="19">
+      <c r="J236" s="45">
         <f t="shared" si="21"/>
         <v>0.00021</v>
       </c>
@@ -15048,7 +15052,7 @@
         <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="L236" s="19">
+      <c r="L236" s="45">
         <f t="shared" si="23"/>
         <v>0.0042</v>
       </c>
@@ -15082,7 +15086,7 @@
         <f>PRODUCT($B$38,$C$42,$D$42,$E$42,($F$45-$F$38-$F$42))</f>
         <v>1344</v>
       </c>
-      <c r="J237" s="19">
+      <c r="J237" s="45">
         <f t="shared" si="21"/>
         <v>0.00042</v>
       </c>
@@ -15090,7 +15094,7 @@
         <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="L237" s="19">
+      <c r="L237" s="45">
         <f t="shared" si="23"/>
         <v>0.0084</v>
       </c>
@@ -15124,7 +15128,7 @@
         <f>PRODUCT($B$42,$C$38,$D$38,$E$38,($F$45-$F$38-$F$42))</f>
         <v>560</v>
       </c>
-      <c r="J238" s="19">
+      <c r="J238" s="45">
         <f t="shared" si="21"/>
         <v>0.000175</v>
       </c>
@@ -15132,7 +15136,7 @@
         <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="L238" s="19">
+      <c r="L238" s="45">
         <f t="shared" si="23"/>
         <v>0.0035</v>
       </c>
@@ -15166,7 +15170,7 @@
         <f>PRODUCT($B$42,$C$38,$D$38,$E$42,($F$45-$F$38-$F$42))</f>
         <v>1120</v>
       </c>
-      <c r="J239" s="19">
+      <c r="J239" s="45">
         <f t="shared" si="21"/>
         <v>0.00035</v>
       </c>
@@ -15174,7 +15178,7 @@
         <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="L239" s="19">
+      <c r="L239" s="45">
         <f t="shared" si="23"/>
         <v>0.007</v>
       </c>
@@ -15208,7 +15212,7 @@
         <f>PRODUCT($B$42,$C$38,$D$42,$E$38,($F$45-$F$38-$F$42))</f>
         <v>1120</v>
       </c>
-      <c r="J240" s="19">
+      <c r="J240" s="45">
         <f t="shared" si="21"/>
         <v>0.00035</v>
       </c>
@@ -15216,7 +15220,7 @@
         <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="L240" s="19">
+      <c r="L240" s="45">
         <f t="shared" si="23"/>
         <v>0.007</v>
       </c>
@@ -15250,7 +15254,7 @@
         <f>PRODUCT($B$42,$C$38,$D$42,$E$42,($F$45-$F$38-$F$42))</f>
         <v>2240</v>
       </c>
-      <c r="J241" s="19">
+      <c r="J241" s="45">
         <f t="shared" si="21"/>
         <v>0.0007</v>
       </c>
@@ -15258,7 +15262,7 @@
         <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="L241" s="19">
+      <c r="L241" s="45">
         <f t="shared" si="23"/>
         <v>0.014</v>
       </c>
@@ -15292,7 +15296,7 @@
         <f>PRODUCT($B$42,$C$42,$D$38,$E$38,($F$45-$F$38-$F$42))</f>
         <v>840</v>
       </c>
-      <c r="J242" s="19">
+      <c r="J242" s="45">
         <f t="shared" si="21"/>
         <v>0.0002625</v>
       </c>
@@ -15300,7 +15304,7 @@
         <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="L242" s="19">
+      <c r="L242" s="45">
         <f t="shared" si="23"/>
         <v>0.00525</v>
       </c>
@@ -15334,7 +15338,7 @@
         <f>PRODUCT($B$42,$C$42,$D$38,$E$42,($F$45-$F$38-$F$42))</f>
         <v>1680</v>
       </c>
-      <c r="J243" s="19">
+      <c r="J243" s="45">
         <f t="shared" si="21"/>
         <v>0.000525</v>
       </c>
@@ -15342,7 +15346,7 @@
         <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="L243" s="19">
+      <c r="L243" s="45">
         <f t="shared" si="23"/>
         <v>0.0105</v>
       </c>
@@ -15376,7 +15380,7 @@
         <f>PRODUCT($B$42,$C$42,$D$42,$E$38,($F$45-$F$38-$F$42))</f>
         <v>1680</v>
       </c>
-      <c r="J244" s="19">
+      <c r="J244" s="45">
         <f t="shared" si="21"/>
         <v>0.000525</v>
       </c>
@@ -15384,7 +15388,7 @@
         <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="L244" s="19">
+      <c r="L244" s="45">
         <f t="shared" si="23"/>
         <v>0.0105</v>
       </c>
@@ -15418,7 +15422,7 @@
         <f>PRODUCT($B$38,$C$38,$D$42,($E$45-$E$38-$E$42),$F$45)</f>
         <v>4480</v>
       </c>
-      <c r="J245" s="19">
+      <c r="J245" s="45">
         <f t="shared" ref="J245:J279" si="27">I245/$B$48</f>
         <v>0.0014</v>
       </c>
@@ -15426,7 +15430,7 @@
         <f t="shared" ref="K245:K250" si="28">MAX(0,INDEX($B$3:$D$7,MATCH($B245,$A$3:$A$7,0),MATCH($C245,$B$2:$D$2,0)))</f>
         <v>5</v>
       </c>
-      <c r="L245" s="19">
+      <c r="L245" s="45">
         <f t="shared" ref="L245:L279" si="29">J245*K245</f>
         <v>0.007</v>
       </c>
@@ -15460,7 +15464,7 @@
         <f>PRODUCT($B$38,$C$42,$D$38,($E$45-$E$38-$E$42),$F$45)</f>
         <v>3360</v>
       </c>
-      <c r="J246" s="19">
+      <c r="J246" s="45">
         <f t="shared" si="27"/>
         <v>0.00105</v>
       </c>
@@ -15468,7 +15472,7 @@
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="L246" s="19">
+      <c r="L246" s="45">
         <f t="shared" si="29"/>
         <v>0.00525</v>
       </c>
@@ -15502,7 +15506,7 @@
         <f>PRODUCT($B$38,$C$42,$D$42,($E$45-$E$38-$E$42),$F$45)</f>
         <v>6720</v>
       </c>
-      <c r="J247" s="19">
+      <c r="J247" s="45">
         <f t="shared" si="27"/>
         <v>0.0021</v>
       </c>
@@ -15510,7 +15514,7 @@
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="L247" s="19">
+      <c r="L247" s="45">
         <f t="shared" si="29"/>
         <v>0.0105</v>
       </c>
@@ -15544,7 +15548,7 @@
         <f>PRODUCT($B$42,$C$38,$D$38,($E$45-$E$38-$E$42),$F$45)</f>
         <v>5600</v>
       </c>
-      <c r="J248" s="19">
+      <c r="J248" s="45">
         <f t="shared" si="27"/>
         <v>0.00175</v>
       </c>
@@ -15552,7 +15556,7 @@
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="L248" s="19">
+      <c r="L248" s="45">
         <f t="shared" si="29"/>
         <v>0.00875</v>
       </c>
@@ -15586,7 +15590,7 @@
         <f>PRODUCT($B$42,$C$38,$D$42,($E$45-$E$38-$E$42),$F$45)</f>
         <v>11200</v>
       </c>
-      <c r="J249" s="19">
+      <c r="J249" s="45">
         <f t="shared" si="27"/>
         <v>0.0035</v>
       </c>
@@ -15594,7 +15598,7 @@
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="L249" s="19">
+      <c r="L249" s="45">
         <f t="shared" si="29"/>
         <v>0.0175</v>
       </c>
@@ -15628,7 +15632,7 @@
         <f>PRODUCT($B$42,$C$42,$D$38,($E$45-$E$38-$E$42),$F$45)</f>
         <v>8400</v>
       </c>
-      <c r="J250" s="19">
+      <c r="J250" s="45">
         <f t="shared" si="27"/>
         <v>0.002625</v>
       </c>
@@ -15636,7 +15640,7 @@
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="L250" s="19">
+      <c r="L250" s="45">
         <f t="shared" si="29"/>
         <v>0.013125</v>
       </c>
@@ -15670,7 +15674,7 @@
         <f>PRODUCT($B$38,$C$38,$D$43,$E$38,$F$38)</f>
         <v>64</v>
       </c>
-      <c r="J251" s="19">
+      <c r="J251" s="45">
         <f t="shared" si="27"/>
         <v>2e-5</v>
       </c>
@@ -15678,7 +15682,7 @@
         <f t="shared" ref="K251:K277" si="30">MAX(0,INDEX($B$3:$D$7,MATCH($B251,$A$3:$A$7,0),MATCH($C251,$B$2:$D$2,0)))</f>
         <v>50</v>
       </c>
-      <c r="L251" s="19">
+      <c r="L251" s="45">
         <f t="shared" si="29"/>
         <v>0.001</v>
       </c>
@@ -15712,7 +15716,7 @@
         <f>PRODUCT($B$38,$C$38,$D$43,$E$38,$F$43)</f>
         <v>128</v>
       </c>
-      <c r="J252" s="19">
+      <c r="J252" s="45">
         <f t="shared" si="27"/>
         <v>4e-5</v>
       </c>
@@ -15720,7 +15724,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L252" s="19">
+      <c r="L252" s="45">
         <f t="shared" si="29"/>
         <v>0.002</v>
       </c>
@@ -15754,7 +15758,7 @@
         <f>PRODUCT($B$38,$C$38,$D$43,$E$43,$F$38)</f>
         <v>128</v>
       </c>
-      <c r="J253" s="19">
+      <c r="J253" s="45">
         <f t="shared" si="27"/>
         <v>4e-5</v>
       </c>
@@ -15762,7 +15766,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L253" s="19">
+      <c r="L253" s="45">
         <f t="shared" si="29"/>
         <v>0.002</v>
       </c>
@@ -15796,7 +15800,7 @@
         <f>PRODUCT($B$38,$C$38,$D$43,$E$43,$F$43)</f>
         <v>256</v>
       </c>
-      <c r="J254" s="19">
+      <c r="J254" s="45">
         <f t="shared" si="27"/>
         <v>8e-5</v>
       </c>
@@ -15804,7 +15808,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L254" s="19">
+      <c r="L254" s="45">
         <f t="shared" si="29"/>
         <v>0.004</v>
       </c>
@@ -15838,7 +15842,7 @@
         <f>PRODUCT($B$38,$C$43,$D$38,$E$38,$F$38)</f>
         <v>64</v>
       </c>
-      <c r="J255" s="19">
+      <c r="J255" s="45">
         <f t="shared" si="27"/>
         <v>2e-5</v>
       </c>
@@ -15846,7 +15850,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L255" s="19">
+      <c r="L255" s="45">
         <f t="shared" si="29"/>
         <v>0.001</v>
       </c>
@@ -15880,7 +15884,7 @@
         <f>PRODUCT($B$38,$C$43,$D$38,$E$38,$F$43)</f>
         <v>128</v>
       </c>
-      <c r="J256" s="19">
+      <c r="J256" s="45">
         <f t="shared" si="27"/>
         <v>4e-5</v>
       </c>
@@ -15888,7 +15892,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L256" s="19">
+      <c r="L256" s="45">
         <f t="shared" si="29"/>
         <v>0.002</v>
       </c>
@@ -15922,7 +15926,7 @@
         <f>PRODUCT($B$38,$C$43,$D$38,$E$43,$F$38)</f>
         <v>128</v>
       </c>
-      <c r="J257" s="19">
+      <c r="J257" s="45">
         <f t="shared" si="27"/>
         <v>4e-5</v>
       </c>
@@ -15930,7 +15934,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L257" s="19">
+      <c r="L257" s="45">
         <f t="shared" si="29"/>
         <v>0.002</v>
       </c>
@@ -15964,7 +15968,7 @@
         <f>PRODUCT($B$38,$C$43,$D$38,$E$43,$F$43)</f>
         <v>256</v>
       </c>
-      <c r="J258" s="19">
+      <c r="J258" s="45">
         <f t="shared" si="27"/>
         <v>8e-5</v>
       </c>
@@ -15972,7 +15976,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L258" s="19">
+      <c r="L258" s="45">
         <f t="shared" si="29"/>
         <v>0.004</v>
       </c>
@@ -16006,7 +16010,7 @@
         <f>PRODUCT($B$38,$C$43,$D$43,$E$38,$F$38)</f>
         <v>128</v>
       </c>
-      <c r="J259" s="19">
+      <c r="J259" s="45">
         <f t="shared" si="27"/>
         <v>4e-5</v>
       </c>
@@ -16014,7 +16018,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L259" s="19">
+      <c r="L259" s="45">
         <f t="shared" si="29"/>
         <v>0.002</v>
       </c>
@@ -16048,7 +16052,7 @@
         <f>PRODUCT($B$38,$C$43,$D$43,$E$38,$F$43)</f>
         <v>256</v>
       </c>
-      <c r="J260" s="19">
+      <c r="J260" s="45">
         <f t="shared" si="27"/>
         <v>8e-5</v>
       </c>
@@ -16056,7 +16060,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L260" s="19">
+      <c r="L260" s="45">
         <f t="shared" si="29"/>
         <v>0.004</v>
       </c>
@@ -16090,7 +16094,7 @@
         <f>PRODUCT($B$38,$C$43,$D$43,$E$43,$F$38)</f>
         <v>256</v>
       </c>
-      <c r="J261" s="19">
+      <c r="J261" s="45">
         <f t="shared" si="27"/>
         <v>8e-5</v>
       </c>
@@ -16098,7 +16102,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L261" s="19">
+      <c r="L261" s="45">
         <f t="shared" si="29"/>
         <v>0.004</v>
       </c>
@@ -16132,7 +16136,7 @@
         <f>PRODUCT($B$38,$C$43,$D$43,$E$43,$F$43)</f>
         <v>512</v>
       </c>
-      <c r="J262" s="19">
+      <c r="J262" s="45">
         <f t="shared" si="27"/>
         <v>0.00016</v>
       </c>
@@ -16140,7 +16144,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L262" s="19">
+      <c r="L262" s="45">
         <f t="shared" si="29"/>
         <v>0.008</v>
       </c>
@@ -16174,7 +16178,7 @@
         <f>PRODUCT($B$43,$C$38,$D$38,$E$38,$F$38)</f>
         <v>96</v>
       </c>
-      <c r="J263" s="19">
+      <c r="J263" s="45">
         <f t="shared" si="27"/>
         <v>3e-5</v>
       </c>
@@ -16182,7 +16186,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L263" s="19">
+      <c r="L263" s="45">
         <f t="shared" si="29"/>
         <v>0.0015</v>
       </c>
@@ -16216,7 +16220,7 @@
         <f>PRODUCT($B$43,$C$38,$D$38,$E$38,$F$43)</f>
         <v>192</v>
       </c>
-      <c r="J264" s="19">
+      <c r="J264" s="45">
         <f t="shared" si="27"/>
         <v>6e-5</v>
       </c>
@@ -16224,7 +16228,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L264" s="19">
+      <c r="L264" s="45">
         <f t="shared" si="29"/>
         <v>0.003</v>
       </c>
@@ -16258,7 +16262,7 @@
         <f>PRODUCT($B$43,$C$38,$D$38,$E$43,$F$38)</f>
         <v>192</v>
       </c>
-      <c r="J265" s="19">
+      <c r="J265" s="45">
         <f t="shared" si="27"/>
         <v>6e-5</v>
       </c>
@@ -16266,7 +16270,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L265" s="19">
+      <c r="L265" s="45">
         <f t="shared" si="29"/>
         <v>0.003</v>
       </c>
@@ -16300,7 +16304,7 @@
         <f>PRODUCT($B$43,$C$38,$D$38,$E$43,$F$43)</f>
         <v>384</v>
       </c>
-      <c r="J266" s="19">
+      <c r="J266" s="45">
         <f t="shared" si="27"/>
         <v>0.00012</v>
       </c>
@@ -16308,7 +16312,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L266" s="19">
+      <c r="L266" s="45">
         <f t="shared" si="29"/>
         <v>0.006</v>
       </c>
@@ -16342,7 +16346,7 @@
         <f>PRODUCT($B$43,$C$38,$D$43,$E$38,$F$38)</f>
         <v>192</v>
       </c>
-      <c r="J267" s="19">
+      <c r="J267" s="45">
         <f t="shared" si="27"/>
         <v>6e-5</v>
       </c>
@@ -16350,7 +16354,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L267" s="19">
+      <c r="L267" s="45">
         <f t="shared" si="29"/>
         <v>0.003</v>
       </c>
@@ -16384,7 +16388,7 @@
         <f>PRODUCT($B$43,$C$38,$D$43,$E$38,$F$43)</f>
         <v>384</v>
       </c>
-      <c r="J268" s="19">
+      <c r="J268" s="45">
         <f t="shared" si="27"/>
         <v>0.00012</v>
       </c>
@@ -16392,7 +16396,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L268" s="19">
+      <c r="L268" s="45">
         <f t="shared" si="29"/>
         <v>0.006</v>
       </c>
@@ -16426,7 +16430,7 @@
         <f>PRODUCT($B$43,$C$38,$D$43,$E$43,$F$38)</f>
         <v>384</v>
       </c>
-      <c r="J269" s="19">
+      <c r="J269" s="45">
         <f t="shared" si="27"/>
         <v>0.00012</v>
       </c>
@@ -16434,7 +16438,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L269" s="19">
+      <c r="L269" s="45">
         <f t="shared" si="29"/>
         <v>0.006</v>
       </c>
@@ -16468,7 +16472,7 @@
         <f>PRODUCT($B$43,$C$38,$D$43,$E$43,$F$43)</f>
         <v>768</v>
       </c>
-      <c r="J270" s="19">
+      <c r="J270" s="45">
         <f t="shared" si="27"/>
         <v>0.00024</v>
       </c>
@@ -16476,7 +16480,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L270" s="19">
+      <c r="L270" s="45">
         <f t="shared" si="29"/>
         <v>0.012</v>
       </c>
@@ -16510,7 +16514,7 @@
         <f>PRODUCT($B$43,$C$43,$D$38,$E$38,$F$38)</f>
         <v>192</v>
       </c>
-      <c r="J271" s="19">
+      <c r="J271" s="45">
         <f t="shared" si="27"/>
         <v>6e-5</v>
       </c>
@@ -16518,7 +16522,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L271" s="19">
+      <c r="L271" s="45">
         <f t="shared" si="29"/>
         <v>0.003</v>
       </c>
@@ -16552,7 +16556,7 @@
         <f>PRODUCT($B$43,$C$43,$D$38,$E$38,$F$43)</f>
         <v>384</v>
       </c>
-      <c r="J272" s="19">
+      <c r="J272" s="45">
         <f t="shared" si="27"/>
         <v>0.00012</v>
       </c>
@@ -16560,7 +16564,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L272" s="19">
+      <c r="L272" s="45">
         <f t="shared" si="29"/>
         <v>0.006</v>
       </c>
@@ -16594,7 +16598,7 @@
         <f>PRODUCT($B$43,$C$43,$D$38,$E$43,$F$38)</f>
         <v>384</v>
       </c>
-      <c r="J273" s="19">
+      <c r="J273" s="45">
         <f t="shared" si="27"/>
         <v>0.00012</v>
       </c>
@@ -16602,7 +16606,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L273" s="19">
+      <c r="L273" s="45">
         <f t="shared" si="29"/>
         <v>0.006</v>
       </c>
@@ -16636,7 +16640,7 @@
         <f>PRODUCT($B$43,$C$43,$D$38,$E$43,$F$43)</f>
         <v>768</v>
       </c>
-      <c r="J274" s="19">
+      <c r="J274" s="45">
         <f t="shared" si="27"/>
         <v>0.00024</v>
       </c>
@@ -16644,7 +16648,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L274" s="19">
+      <c r="L274" s="45">
         <f t="shared" si="29"/>
         <v>0.012</v>
       </c>
@@ -16678,7 +16682,7 @@
         <f>PRODUCT($B$43,$C$43,$D$43,$E$38,$F$38)</f>
         <v>384</v>
       </c>
-      <c r="J275" s="19">
+      <c r="J275" s="45">
         <f t="shared" si="27"/>
         <v>0.00012</v>
       </c>
@@ -16686,7 +16690,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L275" s="19">
+      <c r="L275" s="45">
         <f t="shared" si="29"/>
         <v>0.006</v>
       </c>
@@ -16720,7 +16724,7 @@
         <f>PRODUCT($B$43,$C$43,$D$43,$E$38,$F$43)</f>
         <v>768</v>
       </c>
-      <c r="J276" s="19">
+      <c r="J276" s="45">
         <f t="shared" si="27"/>
         <v>0.00024</v>
       </c>
@@ -16728,7 +16732,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L276" s="19">
+      <c r="L276" s="45">
         <f t="shared" si="29"/>
         <v>0.012</v>
       </c>
@@ -16762,7 +16766,7 @@
         <f>PRODUCT($B$43,$C$43,$D$43,$E$43,$F$38)</f>
         <v>768</v>
       </c>
-      <c r="J277" s="19">
+      <c r="J277" s="45">
         <f t="shared" si="27"/>
         <v>0.00024</v>
       </c>
@@ -16770,7 +16774,7 @@
         <f t="shared" si="30"/>
         <v>50</v>
       </c>
-      <c r="L277" s="19">
+      <c r="L277" s="45">
         <f t="shared" si="29"/>
         <v>0.012</v>
       </c>
@@ -16804,7 +16808,7 @@
         <f>PRODUCT($B$38,$C$38,$D$43,$E$38,($F$45-$F$38-$F$43))</f>
         <v>448</v>
       </c>
-      <c r="J278" s="19">
+      <c r="J278" s="45">
         <f t="shared" ref="J278:J300" si="31">I278/$B$48</f>
         <v>0.00014</v>
       </c>
@@ -16812,7 +16816,7 @@
         <f t="shared" ref="K278:K290" si="32">MAX(0,INDEX($B$3:$D$7,MATCH($B278,$A$3:$A$7,0),MATCH($C278,$B$2:$D$2,0)))</f>
         <v>10</v>
       </c>
-      <c r="L278" s="19">
+      <c r="L278" s="45">
         <f t="shared" ref="L278:L300" si="33">J278*K278</f>
         <v>0.0014</v>
       </c>
@@ -16846,7 +16850,7 @@
         <f>PRODUCT($B$38,$C$38,$D$43,$E$43,($F$45-$F$38-$F$43))</f>
         <v>896</v>
       </c>
-      <c r="J279" s="19">
+      <c r="J279" s="45">
         <f t="shared" si="31"/>
         <v>0.00028</v>
       </c>
@@ -16854,7 +16858,7 @@
         <f t="shared" si="32"/>
         <v>10</v>
       </c>
-      <c r="L279" s="19">
+      <c r="L279" s="45">
         <f t="shared" si="33"/>
         <v>0.0028</v>
       </c>
@@ -16888,7 +16892,7 @@
         <f>PRODUCT($B$38,$C$43,$D$38,$E$38,($F$45-$F$38-$F$43))</f>
         <v>448</v>
       </c>
-      <c r="J280" s="19">
+      <c r="J280" s="45">
         <f t="shared" si="31"/>
         <v>0.00014</v>
       </c>
@@ -16896,7 +16900,7 @@
         <f t="shared" si="32"/>
         <v>10</v>
       </c>
-      <c r="L280" s="19">
+      <c r="L280" s="45">
         <f t="shared" si="33"/>
         <v>0.0014</v>
       </c>
@@ -16930,7 +16934,7 @@
         <f>PRODUCT($B$38,$C$43,$D$38,$E$43,($F$45-$F$38-$F$43))</f>
         <v>896</v>
       </c>
-      <c r="J281" s="19">
+      <c r="J281" s="45">
         <f t="shared" si="31"/>
         <v>0.00028</v>
       </c>
@@ -16938,7 +16942,7 @@
         <f t="shared" si="32"/>
         <v>10</v>
       </c>
-      <c r="L281" s="19">
+      <c r="L281" s="45">
         <f t="shared" si="33"/>
         <v>0.0028</v>
       </c>
@@ -16972,7 +16976,7 @@
         <f>PRODUCT($B$38,$C$43,$D$43,$E$38,($F$45-$F$38-$F$43))</f>
         <v>896</v>
       </c>
-      <c r="J282" s="19">
+      <c r="J282" s="45">
         <f t="shared" si="31"/>
         <v>0.00028</v>
       </c>
@@ -16980,7 +16984,7 @@
         <f t="shared" si="32"/>
         <v>10</v>
       </c>
-      <c r="L282" s="19">
+      <c r="L282" s="45">
         <f t="shared" si="33"/>
         <v>0.0028</v>
       </c>
@@ -17014,7 +17018,7 @@
         <f>PRODUCT($B$38,$C$43,$D$43,$E$43,($F$45-$F$38-$F$43))</f>
         <v>1792</v>
       </c>
-      <c r="J283" s="19">
+      <c r="J283" s="45">
         <f t="shared" si="31"/>
         <v>0.00056</v>
       </c>
@@ -17022,7 +17026,7 @@
         <f t="shared" si="32"/>
         <v>10</v>
       </c>
-      <c r="L283" s="19">
+      <c r="L283" s="45">
         <f t="shared" si="33"/>
         <v>0.0056</v>
       </c>
@@ -17056,7 +17060,7 @@
         <f>PRODUCT($B$43,$C$38,$D$38,$E$38,($F$45-$F$38-$F$43))</f>
         <v>672</v>
       </c>
-      <c r="J284" s="19">
+      <c r="J284" s="45">
         <f t="shared" si="31"/>
         <v>0.00021</v>
       </c>
@@ -17064,7 +17068,7 @@
         <f t="shared" si="32"/>
         <v>10</v>
       </c>
-      <c r="L284" s="19">
+      <c r="L284" s="45">
         <f t="shared" si="33"/>
         <v>0.0021</v>
       </c>
@@ -17098,7 +17102,7 @@
         <f>PRODUCT($B$43,$C$38,$D$38,$E$43,($F$45-$F$38-$F$43))</f>
         <v>1344</v>
       </c>
-      <c r="J285" s="19">
+      <c r="J285" s="45">
         <f t="shared" si="31"/>
         <v>0.00042</v>
       </c>
@@ -17106,7 +17110,7 @@
         <f t="shared" si="32"/>
         <v>10</v>
       </c>
-      <c r="L285" s="19">
+      <c r="L285" s="45">
         <f t="shared" si="33"/>
         <v>0.0042</v>
       </c>
@@ -17140,7 +17144,7 @@
         <f>PRODUCT($B$43,$C$38,$D$43,$E$38,($F$45-$F$38-$F$43))</f>
         <v>1344</v>
       </c>
-      <c r="J286" s="19">
+      <c r="J286" s="45">
         <f t="shared" si="31"/>
         <v>0.00042</v>
       </c>
@@ -17148,7 +17152,7 @@
         <f t="shared" si="32"/>
         <v>10</v>
       </c>
-      <c r="L286" s="19">
+      <c r="L286" s="45">
         <f t="shared" si="33"/>
         <v>0.0042</v>
       </c>
@@ -17182,7 +17186,7 @@
         <f>PRODUCT($B$43,$C$38,$D$43,$E$43,($F$45-$F$38-$F$43))</f>
         <v>2688</v>
       </c>
-      <c r="J287" s="19">
+      <c r="J287" s="45">
         <f t="shared" si="31"/>
         <v>0.00084</v>
       </c>
@@ -17190,7 +17194,7 @@
         <f t="shared" si="32"/>
         <v>10</v>
       </c>
-      <c r="L287" s="19">
+      <c r="L287" s="45">
         <f t="shared" si="33"/>
         <v>0.0084</v>
       </c>
@@ -17224,7 +17228,7 @@
         <f>PRODUCT($B$43,$C$43,$D$38,$E$38,($F$45-$F$38-$F$43))</f>
         <v>1344</v>
       </c>
-      <c r="J288" s="19">
+      <c r="J288" s="45">
         <f t="shared" si="31"/>
         <v>0.00042</v>
       </c>
@@ -17232,7 +17236,7 @@
         <f t="shared" si="32"/>
         <v>10</v>
       </c>
-      <c r="L288" s="19">
+      <c r="L288" s="45">
         <f t="shared" si="33"/>
         <v>0.0042</v>
       </c>
@@ -17266,7 +17270,7 @@
         <f>PRODUCT($B$43,$C$43,$D$38,$E$43,($F$45-$F$38-$F$43))</f>
         <v>2688</v>
       </c>
-      <c r="J289" s="19">
+      <c r="J289" s="45">
         <f t="shared" si="31"/>
         <v>0.00084</v>
       </c>
@@ -17274,7 +17278,7 @@
         <f t="shared" si="32"/>
         <v>10</v>
       </c>
-      <c r="L289" s="19">
+      <c r="L289" s="45">
         <f t="shared" si="33"/>
         <v>0.0084</v>
       </c>
@@ -17308,7 +17312,7 @@
         <f>PRODUCT($B$43,$C$43,$D$43,$E$38,($F$45-$F$38-$F$43))</f>
         <v>2688</v>
       </c>
-      <c r="J290" s="19">
+      <c r="J290" s="45">
         <f t="shared" si="31"/>
         <v>0.00084</v>
       </c>
@@ -17316,7 +17320,7 @@
         <f t="shared" si="32"/>
         <v>10</v>
       </c>
-      <c r="L290" s="19">
+      <c r="L290" s="45">
         <f t="shared" si="33"/>
         <v>0.0084</v>
       </c>
@@ -17350,7 +17354,7 @@
         <f>PRODUCT($B$38,$C$38,$D$43,($E$45-$E$38-$E$43),$F$45)</f>
         <v>4480</v>
       </c>
-      <c r="J291" s="19">
+      <c r="J291" s="45">
         <f t="shared" si="31"/>
         <v>0.0014</v>
       </c>
@@ -17358,7 +17362,7 @@
         <f t="shared" ref="K291:K296" si="34">MAX(0,INDEX($B$3:$D$7,MATCH($B291,$A$3:$A$7,0),MATCH($C291,$B$2:$D$2,0)))</f>
         <v>5</v>
       </c>
-      <c r="L291" s="19">
+      <c r="L291" s="45">
         <f t="shared" si="33"/>
         <v>0.007</v>
       </c>
@@ -17392,7 +17396,7 @@
         <f>PRODUCT($B$38,$C$43,$D$38,($E$45-$E$38-$E$43),$F$45)</f>
         <v>4480</v>
       </c>
-      <c r="J292" s="19">
+      <c r="J292" s="45">
         <f t="shared" si="31"/>
         <v>0.0014</v>
       </c>
@@ -17400,7 +17404,7 @@
         <f t="shared" si="34"/>
         <v>5</v>
       </c>
-      <c r="L292" s="19">
+      <c r="L292" s="45">
         <f t="shared" si="33"/>
         <v>0.007</v>
       </c>
@@ -17434,7 +17438,7 @@
         <f>PRODUCT($B$38,$C$43,$D$43,($E$45-$E$38-$E$43),$F$45)</f>
         <v>8960</v>
       </c>
-      <c r="J293" s="19">
+      <c r="J293" s="45">
         <f t="shared" si="31"/>
         <v>0.0028</v>
       </c>
@@ -17442,7 +17446,7 @@
         <f t="shared" si="34"/>
         <v>5</v>
       </c>
-      <c r="L293" s="19">
+      <c r="L293" s="45">
         <f t="shared" si="33"/>
         <v>0.014</v>
       </c>
@@ -17476,7 +17480,7 @@
         <f>PRODUCT($B$43,$C$38,$D$38,($E$45-$E$38-$E$43),$F$45)</f>
         <v>6720</v>
       </c>
-      <c r="J294" s="19">
+      <c r="J294" s="45">
         <f t="shared" si="31"/>
         <v>0.0021</v>
       </c>
@@ -17484,7 +17488,7 @@
         <f t="shared" si="34"/>
         <v>5</v>
       </c>
-      <c r="L294" s="19">
+      <c r="L294" s="45">
         <f t="shared" si="33"/>
         <v>0.0105</v>
       </c>
@@ -17518,7 +17522,7 @@
         <f>PRODUCT($B$43,$C$38,$D$43,($E$45-$E$38-$E$43),$F$45)</f>
         <v>13440</v>
       </c>
-      <c r="J295" s="19">
+      <c r="J295" s="45">
         <f t="shared" si="31"/>
         <v>0.0042</v>
       </c>
@@ -17526,7 +17530,7 @@
         <f t="shared" si="34"/>
         <v>5</v>
       </c>
-      <c r="L295" s="19">
+      <c r="L295" s="45">
         <f t="shared" si="33"/>
         <v>0.021</v>
       </c>
@@ -17560,7 +17564,7 @@
         <f>PRODUCT($B$43,$C$43,$D$38,($E$45-$E$38-$E$43),$F$45)</f>
         <v>13440</v>
       </c>
-      <c r="J296" s="19">
+      <c r="J296" s="45">
         <f t="shared" si="31"/>
         <v>0.0042</v>
       </c>
@@ -17568,7 +17572,7 @@
         <f t="shared" si="34"/>
         <v>5</v>
       </c>
-      <c r="L296" s="19">
+      <c r="L296" s="45">
         <f t="shared" si="33"/>
         <v>0.021</v>
       </c>
@@ -17602,7 +17606,7 @@
         <f>PRODUCT($B$38,$C$38,$D$38,$E$38,$F$38)</f>
         <v>32</v>
       </c>
-      <c r="J297" s="19">
+      <c r="J297" s="45">
         <f t="shared" si="31"/>
         <v>1e-5</v>
       </c>
@@ -17610,7 +17614,7 @@
         <f>INDEX($B$8:$D$8,1,3)</f>
         <v>1000</v>
       </c>
-      <c r="L297" s="19">
+      <c r="L297" s="45">
         <f t="shared" si="33"/>
         <v>0.01</v>
       </c>
@@ -17644,7 +17648,7 @@
         <f>2*2*2*2*18</f>
         <v>288</v>
       </c>
-      <c r="J298" s="19">
+      <c r="J298" s="45">
         <f t="shared" si="31"/>
         <v>9e-5</v>
       </c>
@@ -17652,7 +17656,7 @@
         <f>INDEX($B$8:$D$8,1,2)</f>
         <v>300</v>
       </c>
-      <c r="L298" s="19">
+      <c r="L298" s="45">
         <f t="shared" si="33"/>
         <v>0.027</v>
       </c>
@@ -17686,7 +17690,7 @@
         <f>2*2*2*18*20</f>
         <v>2880</v>
       </c>
-      <c r="J299" s="19">
+      <c r="J299" s="45">
         <f t="shared" si="31"/>
         <v>0.0009</v>
       </c>
@@ -17694,7 +17698,7 @@
         <f>INDEX($B$8:$D$8,1,1)</f>
         <v>150</v>
       </c>
-      <c r="L299" s="19">
+      <c r="L299" s="45">
         <f t="shared" si="33"/>
         <v>0.135</v>
       </c>
@@ -17734,7 +17738,7 @@
       <c r="K300" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="L300" s="22">
+      <c r="L300" s="46">
         <f>SUM(L52:L299)</f>
         <v>1.630853125</v>
       </c>
